--- a/Sales_Customer_Order_Management_Analysis Exersize.xlsx
+++ b/Sales_Customer_Order_Management_Analysis Exersize.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\mini project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{798FAACA-8FBB-4CA5-B374-D1306FED8D31}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A8594D-A8F7-4371-ACAB-70F43530E8F6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1135,7 +1135,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD2D6DC"/>
+        <fgColor rgb="FF00022E"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1182,7 +1182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1248,8 +1248,19 @@
     <xf numFmtId="14" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1260,6 +1271,8 @@
     <mruColors>
       <color rgb="FFD2D6DC"/>
       <color rgb="FF00022E"/>
+      <color rgb="FFFFFFFF"/>
+      <color rgb="FFF8F8F8"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1814,69 +1827,69 @@
       <c r="A2" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="32">
+      <c r="B2" s="33">
         <v>46186</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="31">
+      <c r="E2" s="34">
         <v>36</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="31" t="s">
+      <c r="I2" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="J2" s="31" t="s">
+      <c r="J2" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="K2" s="31">
+      <c r="K2" s="34">
         <v>24</v>
       </c>
-      <c r="L2" s="31">
+      <c r="L2" s="34">
         <v>55000</v>
       </c>
-      <c r="M2" s="31">
+      <c r="M2" s="34">
         <v>0.2</v>
       </c>
-      <c r="N2" s="31" t="s">
+      <c r="N2" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O2" s="31" t="s">
+      <c r="O2" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P2" s="32">
+      <c r="P2" s="33">
         <v>46187</v>
       </c>
-      <c r="Q2" s="31">
+      <c r="Q2" s="34">
         <v>1</v>
       </c>
-      <c r="R2" s="31" t="s">
+      <c r="R2" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S2" s="31" t="s">
+      <c r="S2" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="T2" s="31">
+      <c r="T2" s="34">
         <f t="shared" ref="T2:T33" si="0">K2*L2</f>
         <v>1320000</v>
       </c>
-      <c r="U2" s="31">
+      <c r="U2" s="34">
         <f t="shared" ref="U2:U33" si="1">T2*M2</f>
         <v>264000</v>
       </c>
-      <c r="V2" s="31">
+      <c r="V2" s="34">
         <f t="shared" ref="V2:V33" si="2">T2-U2</f>
         <v>1056000</v>
       </c>
@@ -1885,69 +1898,69 @@
       <c r="A3" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="32">
+      <c r="B3" s="33">
         <v>46078</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E3" s="31">
+      <c r="E3" s="34">
         <v>56</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H3" s="31" t="s">
+      <c r="H3" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I3" s="31" t="s">
+      <c r="I3" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="J3" s="31" t="s">
+      <c r="J3" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="K3" s="31">
+      <c r="K3" s="34">
         <v>8</v>
       </c>
-      <c r="L3" s="31">
+      <c r="L3" s="34">
         <v>250</v>
       </c>
-      <c r="M3" s="31">
+      <c r="M3" s="34">
         <v>0.15</v>
       </c>
-      <c r="N3" s="31" t="s">
+      <c r="N3" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="O3" s="31" t="s">
+      <c r="O3" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P3" s="32">
+      <c r="P3" s="33">
         <v>46080</v>
       </c>
-      <c r="Q3" s="31">
+      <c r="Q3" s="34">
         <v>1</v>
       </c>
-      <c r="R3" s="31" t="s">
+      <c r="R3" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S3" s="31" t="s">
+      <c r="S3" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="T3" s="31">
+      <c r="T3" s="34">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="U3" s="31">
+      <c r="U3" s="34">
         <f t="shared" si="1"/>
         <v>300</v>
       </c>
-      <c r="V3" s="31">
+      <c r="V3" s="34">
         <f t="shared" si="2"/>
         <v>1700</v>
       </c>
@@ -1956,69 +1969,69 @@
       <c r="A4" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="32">
+      <c r="B4" s="33">
         <v>46131</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="34">
         <v>34</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F4" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="31" t="s">
+      <c r="G4" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="31" t="s">
+      <c r="H4" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I4" s="31" t="s">
+      <c r="I4" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J4" s="31" t="s">
+      <c r="J4" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="34">
         <v>13</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="34">
         <v>150</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="34">
         <v>0</v>
       </c>
-      <c r="N4" s="31" t="s">
+      <c r="N4" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="O4" s="31" t="s">
+      <c r="O4" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="P4" s="32">
+      <c r="P4" s="33">
         <v>46134</v>
       </c>
-      <c r="Q4" s="31">
+      <c r="Q4" s="34">
         <v>5</v>
       </c>
-      <c r="R4" s="31" t="s">
+      <c r="R4" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S4" s="31" t="s">
+      <c r="S4" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="T4" s="31">
+      <c r="T4" s="34">
         <f t="shared" si="0"/>
         <v>1950</v>
       </c>
-      <c r="U4" s="31">
+      <c r="U4" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V4" s="31">
+      <c r="V4" s="34">
         <f t="shared" si="2"/>
         <v>1950</v>
       </c>
@@ -2027,69 +2040,69 @@
       <c r="A5" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="33">
         <v>46034</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="34">
         <v>45</v>
       </c>
-      <c r="F5" s="31" t="s">
+      <c r="F5" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="G5" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="31" t="s">
+      <c r="H5" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="31" t="s">
+      <c r="I5" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="J5" s="31" t="s">
+      <c r="J5" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="K5" s="31">
+      <c r="K5" s="34">
         <v>21</v>
       </c>
-      <c r="L5" s="31">
+      <c r="L5" s="34">
         <v>750</v>
       </c>
-      <c r="M5" s="31">
+      <c r="M5" s="34">
         <v>0.2</v>
       </c>
-      <c r="N5" s="31" t="s">
+      <c r="N5" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="O5" s="31" t="s">
+      <c r="O5" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P5" s="32">
+      <c r="P5" s="33">
         <v>46040</v>
       </c>
-      <c r="Q5" s="31">
+      <c r="Q5" s="34">
         <v>1</v>
       </c>
-      <c r="R5" s="31" t="s">
+      <c r="R5" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S5" s="31" t="s">
+      <c r="S5" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="T5" s="31">
+      <c r="T5" s="34">
         <f t="shared" si="0"/>
         <v>15750</v>
       </c>
-      <c r="U5" s="31">
+      <c r="U5" s="34">
         <f t="shared" si="1"/>
         <v>3150</v>
       </c>
-      <c r="V5" s="31">
+      <c r="V5" s="34">
         <f t="shared" si="2"/>
         <v>12600</v>
       </c>
@@ -2098,69 +2111,69 @@
       <c r="A6" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="32">
+      <c r="B6" s="33">
         <v>46081</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="34">
         <v>35</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="G6" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H6" s="31" t="s">
+      <c r="H6" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I6" s="31" t="s">
+      <c r="I6" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="J6" s="31" t="s">
+      <c r="J6" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="K6" s="31">
+      <c r="K6" s="34">
         <v>21</v>
       </c>
-      <c r="L6" s="31">
+      <c r="L6" s="34">
         <v>85</v>
       </c>
-      <c r="M6" s="31">
+      <c r="M6" s="34">
         <v>0.1</v>
       </c>
-      <c r="N6" s="31" t="s">
+      <c r="N6" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O6" s="31" t="s">
+      <c r="O6" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P6" s="32">
+      <c r="P6" s="33">
         <v>46088</v>
       </c>
-      <c r="Q6" s="31">
+      <c r="Q6" s="34">
         <v>2</v>
       </c>
-      <c r="R6" s="31" t="s">
+      <c r="R6" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S6" s="31" t="s">
+      <c r="S6" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="T6" s="31">
+      <c r="T6" s="34">
         <f t="shared" si="0"/>
         <v>1785</v>
       </c>
-      <c r="U6" s="31">
+      <c r="U6" s="34">
         <f t="shared" si="1"/>
         <v>178.5</v>
       </c>
-      <c r="V6" s="31">
+      <c r="V6" s="34">
         <f t="shared" si="2"/>
         <v>1606.5</v>
       </c>
@@ -2169,69 +2182,69 @@
       <c r="A7" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="32">
+      <c r="B7" s="33">
         <v>46262</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="34">
         <v>59</v>
       </c>
-      <c r="F7" s="31" t="s">
+      <c r="F7" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="G7" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="H7" s="31" t="s">
+      <c r="H7" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="31" t="s">
+      <c r="I7" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="J7" s="31" t="s">
+      <c r="J7" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="K7" s="31">
+      <c r="K7" s="34">
         <v>8</v>
       </c>
-      <c r="L7" s="31">
+      <c r="L7" s="34">
         <v>12500</v>
       </c>
-      <c r="M7" s="31">
+      <c r="M7" s="34">
         <v>0.05</v>
       </c>
-      <c r="N7" s="31" t="s">
+      <c r="N7" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="O7" s="31" t="s">
+      <c r="O7" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P7" s="32">
+      <c r="P7" s="33">
         <v>46268</v>
       </c>
-      <c r="Q7" s="31">
+      <c r="Q7" s="34">
         <v>5</v>
       </c>
-      <c r="R7" s="31" t="s">
+      <c r="R7" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S7" s="31" t="s">
+      <c r="S7" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="T7" s="31">
+      <c r="T7" s="34">
         <f t="shared" si="0"/>
         <v>100000</v>
       </c>
-      <c r="U7" s="31">
+      <c r="U7" s="34">
         <f t="shared" si="1"/>
         <v>5000</v>
       </c>
-      <c r="V7" s="31">
+      <c r="V7" s="34">
         <f t="shared" si="2"/>
         <v>95000</v>
       </c>
@@ -2240,69 +2253,69 @@
       <c r="A8" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="33">
         <v>46106</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="34">
         <v>35</v>
       </c>
-      <c r="F8" s="31" t="s">
+      <c r="F8" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="G8" s="31" t="s">
+      <c r="G8" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I8" s="31" t="s">
+      <c r="I8" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="J8" s="31" t="s">
+      <c r="J8" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="K8" s="31">
+      <c r="K8" s="34">
         <v>3</v>
       </c>
-      <c r="L8" s="31">
+      <c r="L8" s="34">
         <v>450</v>
       </c>
-      <c r="M8" s="31">
+      <c r="M8" s="34">
         <v>0.05</v>
       </c>
-      <c r="N8" s="31" t="s">
+      <c r="N8" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="O8" s="31" t="s">
+      <c r="O8" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="P8" s="32">
+      <c r="P8" s="33">
         <v>46113</v>
       </c>
-      <c r="Q8" s="31">
+      <c r="Q8" s="34">
         <v>3</v>
       </c>
-      <c r="R8" s="31" t="s">
+      <c r="R8" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S8" s="31" t="s">
+      <c r="S8" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="T8" s="31">
+      <c r="T8" s="34">
         <f t="shared" si="0"/>
         <v>1350</v>
       </c>
-      <c r="U8" s="31">
+      <c r="U8" s="34">
         <f t="shared" si="1"/>
         <v>67.5</v>
       </c>
-      <c r="V8" s="31">
+      <c r="V8" s="34">
         <f t="shared" si="2"/>
         <v>1282.5</v>
       </c>
@@ -2311,69 +2324,69 @@
       <c r="A9" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="33">
         <v>46150</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="34">
         <v>30</v>
       </c>
-      <c r="F9" s="31" t="s">
+      <c r="F9" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H9" s="31" t="s">
+      <c r="H9" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I9" s="31" t="s">
+      <c r="I9" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="J9" s="31" t="s">
+      <c r="J9" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="K9" s="31">
+      <c r="K9" s="34">
         <v>18</v>
       </c>
-      <c r="L9" s="31">
+      <c r="L9" s="34">
         <v>1200</v>
       </c>
-      <c r="M9" s="31">
+      <c r="M9" s="34">
         <v>0.2</v>
       </c>
-      <c r="N9" s="31" t="s">
+      <c r="N9" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="O9" s="31" t="s">
+      <c r="O9" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="P9" s="32">
+      <c r="P9" s="33">
         <v>46154</v>
       </c>
-      <c r="Q9" s="31">
+      <c r="Q9" s="34">
         <v>4</v>
       </c>
-      <c r="R9" s="31" t="s">
+      <c r="R9" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S9" s="31" t="s">
+      <c r="S9" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="T9" s="31">
+      <c r="T9" s="34">
         <f t="shared" si="0"/>
         <v>21600</v>
       </c>
-      <c r="U9" s="31">
+      <c r="U9" s="34">
         <f t="shared" si="1"/>
         <v>4320</v>
       </c>
-      <c r="V9" s="31">
+      <c r="V9" s="34">
         <f t="shared" si="2"/>
         <v>17280</v>
       </c>
@@ -2382,69 +2395,69 @@
       <c r="A10" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="33">
         <v>46079</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="D10" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="34">
         <v>26</v>
       </c>
-      <c r="F10" s="31" t="s">
+      <c r="F10" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="G10" s="31" t="s">
+      <c r="G10" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="H10" s="31" t="s">
+      <c r="H10" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I10" s="31" t="s">
+      <c r="I10" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="J10" s="31" t="s">
+      <c r="J10" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="K10" s="31">
+      <c r="K10" s="34">
         <v>21</v>
       </c>
-      <c r="L10" s="31">
+      <c r="L10" s="34">
         <v>55000</v>
       </c>
-      <c r="M10" s="31">
+      <c r="M10" s="34">
         <v>0.05</v>
       </c>
-      <c r="N10" s="31" t="s">
+      <c r="N10" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="O10" s="31" t="s">
+      <c r="O10" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P10" s="32">
+      <c r="P10" s="33">
         <v>46081</v>
       </c>
-      <c r="Q10" s="31">
+      <c r="Q10" s="34">
         <v>4</v>
       </c>
-      <c r="R10" s="31" t="s">
+      <c r="R10" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S10" s="31" t="s">
+      <c r="S10" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="T10" s="31">
+      <c r="T10" s="34">
         <f t="shared" si="0"/>
         <v>1155000</v>
       </c>
-      <c r="U10" s="31">
+      <c r="U10" s="34">
         <f t="shared" si="1"/>
         <v>57750</v>
       </c>
-      <c r="V10" s="31">
+      <c r="V10" s="34">
         <f t="shared" si="2"/>
         <v>1097250</v>
       </c>
@@ -2453,69 +2466,69 @@
       <c r="A11" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="33">
         <v>46142</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="C11" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="D11" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="34">
         <v>28</v>
       </c>
-      <c r="F11" s="31" t="s">
+      <c r="F11" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="G11" s="31" t="s">
+      <c r="G11" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="H11" s="31" t="s">
+      <c r="H11" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I11" s="31" t="s">
+      <c r="I11" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="J11" s="31" t="s">
+      <c r="J11" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="K11" s="31">
+      <c r="K11" s="34">
         <v>21</v>
       </c>
-      <c r="L11" s="31">
+      <c r="L11" s="34">
         <v>750</v>
       </c>
-      <c r="M11" s="31">
+      <c r="M11" s="34">
         <v>0.1</v>
       </c>
-      <c r="N11" s="31" t="s">
+      <c r="N11" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="31" t="s">
+      <c r="O11" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P11" s="32">
+      <c r="P11" s="33">
         <v>46147</v>
       </c>
-      <c r="Q11" s="31">
+      <c r="Q11" s="34">
         <v>2</v>
       </c>
-      <c r="R11" s="31" t="s">
+      <c r="R11" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S11" s="31" t="s">
+      <c r="S11" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="T11" s="31">
+      <c r="T11" s="34">
         <f t="shared" si="0"/>
         <v>15750</v>
       </c>
-      <c r="U11" s="31">
+      <c r="U11" s="34">
         <f t="shared" si="1"/>
         <v>1575</v>
       </c>
-      <c r="V11" s="31">
+      <c r="V11" s="34">
         <f t="shared" si="2"/>
         <v>14175</v>
       </c>
@@ -2524,69 +2537,69 @@
       <c r="A12" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="33">
         <v>46207</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="D12" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="34">
         <v>53</v>
       </c>
-      <c r="F12" s="31" t="s">
+      <c r="F12" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="G12" s="31" t="s">
+      <c r="G12" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H12" s="31" t="s">
+      <c r="H12" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I12" s="31" t="s">
+      <c r="I12" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="J12" s="31" t="s">
+      <c r="J12" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="K12" s="31">
+      <c r="K12" s="34">
         <v>21</v>
       </c>
-      <c r="L12" s="31">
+      <c r="L12" s="34">
         <v>750</v>
       </c>
-      <c r="M12" s="31">
+      <c r="M12" s="34">
         <v>0.2</v>
       </c>
-      <c r="N12" s="31" t="s">
+      <c r="N12" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="O12" s="31" t="s">
+      <c r="O12" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P12" s="32">
+      <c r="P12" s="33">
         <v>46213</v>
       </c>
-      <c r="Q12" s="31">
+      <c r="Q12" s="34">
         <v>3</v>
       </c>
-      <c r="R12" s="31" t="s">
+      <c r="R12" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S12" s="31" t="s">
+      <c r="S12" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="T12" s="31">
+      <c r="T12" s="34">
         <f t="shared" si="0"/>
         <v>15750</v>
       </c>
-      <c r="U12" s="31">
+      <c r="U12" s="34">
         <f t="shared" si="1"/>
         <v>3150</v>
       </c>
-      <c r="V12" s="31">
+      <c r="V12" s="34">
         <f t="shared" si="2"/>
         <v>12600</v>
       </c>
@@ -2595,69 +2608,69 @@
       <c r="A13" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="33">
         <v>46222</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="D13" s="31" t="s">
+      <c r="D13" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="34">
         <v>52</v>
       </c>
-      <c r="F13" s="31" t="s">
+      <c r="F13" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="G13" s="31" t="s">
+      <c r="G13" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H13" s="31" t="s">
+      <c r="H13" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I13" s="31" t="s">
+      <c r="I13" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="J13" s="31" t="s">
+      <c r="J13" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="K13" s="31">
+      <c r="K13" s="34">
         <v>10</v>
       </c>
-      <c r="L13" s="31">
+      <c r="L13" s="34">
         <v>650</v>
       </c>
-      <c r="M13" s="31">
+      <c r="M13" s="34">
         <v>0.05</v>
       </c>
-      <c r="N13" s="31" t="s">
+      <c r="N13" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O13" s="31" t="s">
+      <c r="O13" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P13" s="32">
+      <c r="P13" s="33">
         <v>46227</v>
       </c>
-      <c r="Q13" s="31">
+      <c r="Q13" s="34">
         <v>5</v>
       </c>
-      <c r="R13" s="31" t="s">
+      <c r="R13" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S13" s="31" t="s">
+      <c r="S13" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="T13" s="31">
+      <c r="T13" s="34">
         <f t="shared" si="0"/>
         <v>6500</v>
       </c>
-      <c r="U13" s="31">
+      <c r="U13" s="34">
         <f t="shared" si="1"/>
         <v>325</v>
       </c>
-      <c r="V13" s="31">
+      <c r="V13" s="34">
         <f t="shared" si="2"/>
         <v>6175</v>
       </c>
@@ -2666,69 +2679,69 @@
       <c r="A14" s="31" t="s">
         <v>110</v>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="33">
         <v>46210</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="D14" s="31" t="s">
+      <c r="D14" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="34">
         <v>29</v>
       </c>
-      <c r="F14" s="31" t="s">
+      <c r="F14" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="G14" s="31" t="s">
+      <c r="G14" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="H14" s="31" t="s">
+      <c r="H14" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I14" s="31" t="s">
+      <c r="I14" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="J14" s="31" t="s">
+      <c r="J14" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="K14" s="31">
+      <c r="K14" s="34">
         <v>9</v>
       </c>
-      <c r="L14" s="31">
+      <c r="L14" s="34">
         <v>320</v>
       </c>
-      <c r="M14" s="31">
+      <c r="M14" s="34">
         <v>0.2</v>
       </c>
-      <c r="N14" s="31" t="s">
+      <c r="N14" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="O14" s="31" t="s">
+      <c r="O14" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P14" s="32">
+      <c r="P14" s="33">
         <v>46214</v>
       </c>
-      <c r="Q14" s="31">
+      <c r="Q14" s="34">
         <v>2</v>
       </c>
-      <c r="R14" s="31" t="s">
+      <c r="R14" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S14" s="31" t="s">
+      <c r="S14" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="T14" s="31">
+      <c r="T14" s="34">
         <f t="shared" si="0"/>
         <v>2880</v>
       </c>
-      <c r="U14" s="31">
+      <c r="U14" s="34">
         <f t="shared" si="1"/>
         <v>576</v>
       </c>
-      <c r="V14" s="31">
+      <c r="V14" s="34">
         <f t="shared" si="2"/>
         <v>2304</v>
       </c>
@@ -2737,69 +2750,69 @@
       <c r="A15" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="33">
         <v>46102</v>
       </c>
-      <c r="C15" s="31" t="s">
+      <c r="C15" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="D15" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="34">
         <v>49</v>
       </c>
-      <c r="F15" s="31" t="s">
+      <c r="F15" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="G15" s="31" t="s">
+      <c r="G15" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H15" s="31" t="s">
+      <c r="H15" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I15" s="31" t="s">
+      <c r="I15" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J15" s="31" t="s">
+      <c r="J15" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="K15" s="31">
+      <c r="K15" s="34">
         <v>8</v>
       </c>
-      <c r="L15" s="31">
+      <c r="L15" s="34">
         <v>150</v>
       </c>
-      <c r="M15" s="31">
+      <c r="M15" s="34">
         <v>0</v>
       </c>
-      <c r="N15" s="31" t="s">
+      <c r="N15" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="O15" s="31" t="s">
+      <c r="O15" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P15" s="32">
+      <c r="P15" s="33">
         <v>46106</v>
       </c>
-      <c r="Q15" s="31">
+      <c r="Q15" s="34">
         <v>5</v>
       </c>
-      <c r="R15" s="31" t="s">
+      <c r="R15" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S15" s="31" t="s">
+      <c r="S15" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="T15" s="31">
+      <c r="T15" s="34">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="U15" s="31">
+      <c r="U15" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V15" s="31">
+      <c r="V15" s="34">
         <f t="shared" si="2"/>
         <v>1200</v>
       </c>
@@ -2808,67 +2821,67 @@
       <c r="A16" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="B16" s="32">
+      <c r="B16" s="33">
         <v>46079</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="D16" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="34">
         <v>35</v>
       </c>
-      <c r="F16" s="31" t="s">
+      <c r="F16" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="G16" s="31" t="s">
+      <c r="G16" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H16" s="31" t="s">
+      <c r="H16" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I16" s="31" t="s">
+      <c r="I16" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="J16" s="31" t="s">
+      <c r="J16" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="K16" s="31">
+      <c r="K16" s="34">
         <v>17</v>
       </c>
-      <c r="L16" s="31">
+      <c r="L16" s="34">
         <v>650</v>
       </c>
-      <c r="M16" s="31">
+      <c r="M16" s="34">
         <v>0.05</v>
       </c>
-      <c r="N16" s="31" t="s">
+      <c r="N16" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="O16" s="31" t="s">
+      <c r="O16" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P16" s="32">
+      <c r="P16" s="33">
         <v>46080</v>
       </c>
-      <c r="Q16" s="31"/>
-      <c r="R16" s="31" t="s">
+      <c r="Q16" s="34"/>
+      <c r="R16" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S16" s="31" t="s">
+      <c r="S16" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="T16" s="31">
+      <c r="T16" s="34">
         <f t="shared" si="0"/>
         <v>11050</v>
       </c>
-      <c r="U16" s="31">
+      <c r="U16" s="34">
         <f t="shared" si="1"/>
         <v>552.5</v>
       </c>
-      <c r="V16" s="31">
+      <c r="V16" s="34">
         <f t="shared" si="2"/>
         <v>10497.5</v>
       </c>
@@ -2877,69 +2890,69 @@
       <c r="A17" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="33">
         <v>46262</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="C17" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="D17" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="34">
         <v>36</v>
       </c>
-      <c r="F17" s="31" t="s">
+      <c r="F17" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="G17" s="31" t="s">
+      <c r="G17" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="H17" s="31" t="s">
+      <c r="H17" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I17" s="31" t="s">
+      <c r="I17" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="J17" s="31" t="s">
+      <c r="J17" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="K17" s="31">
+      <c r="K17" s="34">
         <v>4</v>
       </c>
-      <c r="L17" s="31">
+      <c r="L17" s="34">
         <v>450</v>
       </c>
-      <c r="M17" s="31">
+      <c r="M17" s="34">
         <v>0</v>
       </c>
-      <c r="N17" s="31" t="s">
+      <c r="N17" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="O17" s="31" t="s">
+      <c r="O17" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P17" s="32">
+      <c r="P17" s="33">
         <v>46267</v>
       </c>
-      <c r="Q17" s="31">
+      <c r="Q17" s="34">
         <v>4</v>
       </c>
-      <c r="R17" s="31" t="s">
+      <c r="R17" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S17" s="31" t="s">
+      <c r="S17" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="T17" s="31">
+      <c r="T17" s="34">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
-      <c r="U17" s="31">
+      <c r="U17" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V17" s="31">
+      <c r="V17" s="34">
         <f t="shared" si="2"/>
         <v>1800</v>
       </c>
@@ -2948,69 +2961,69 @@
       <c r="A18" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="B18" s="32">
+      <c r="B18" s="33">
         <v>46209</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C18" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="34">
         <v>24</v>
       </c>
-      <c r="F18" s="31" t="s">
+      <c r="F18" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="G18" s="31" t="s">
+      <c r="G18" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H18" s="31" t="s">
+      <c r="H18" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I18" s="31" t="s">
+      <c r="I18" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="J18" s="31" t="s">
+      <c r="J18" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="K18" s="31">
+      <c r="K18" s="34">
         <v>4</v>
       </c>
-      <c r="L18" s="31">
+      <c r="L18" s="34">
         <v>750</v>
       </c>
-      <c r="M18" s="31">
+      <c r="M18" s="34">
         <v>0.05</v>
       </c>
-      <c r="N18" s="31" t="s">
+      <c r="N18" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O18" s="31" t="s">
+      <c r="O18" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P18" s="32">
+      <c r="P18" s="33">
         <v>46210</v>
       </c>
-      <c r="Q18" s="31">
+      <c r="Q18" s="34">
         <v>4</v>
       </c>
-      <c r="R18" s="31" t="s">
+      <c r="R18" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S18" s="31" t="s">
+      <c r="S18" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="T18" s="31">
+      <c r="T18" s="34">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="U18" s="31">
+      <c r="U18" s="34">
         <f t="shared" si="1"/>
         <v>150</v>
       </c>
-      <c r="V18" s="31">
+      <c r="V18" s="34">
         <f t="shared" si="2"/>
         <v>2850</v>
       </c>
@@ -3019,69 +3032,69 @@
       <c r="A19" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="B19" s="32">
+      <c r="B19" s="33">
         <v>46069</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="C19" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="D19" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="34">
         <v>25</v>
       </c>
-      <c r="F19" s="31" t="s">
+      <c r="F19" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="G19" s="31" t="s">
+      <c r="G19" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H19" s="31" t="s">
+      <c r="H19" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I19" s="31" t="s">
+      <c r="I19" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="J19" s="31" t="s">
+      <c r="J19" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="K19" s="31">
+      <c r="K19" s="34">
         <v>21</v>
       </c>
-      <c r="L19" s="31">
+      <c r="L19" s="34">
         <v>2200</v>
       </c>
-      <c r="M19" s="31">
+      <c r="M19" s="34">
         <v>0.2</v>
       </c>
-      <c r="N19" s="31" t="s">
+      <c r="N19" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O19" s="31" t="s">
+      <c r="O19" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="P19" s="32">
+      <c r="P19" s="33">
         <v>46072</v>
       </c>
-      <c r="Q19" s="31">
+      <c r="Q19" s="34">
         <v>2</v>
       </c>
-      <c r="R19" s="31" t="s">
+      <c r="R19" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S19" s="31" t="s">
+      <c r="S19" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="T19" s="31">
+      <c r="T19" s="34">
         <f t="shared" si="0"/>
         <v>46200</v>
       </c>
-      <c r="U19" s="31">
+      <c r="U19" s="34">
         <f t="shared" si="1"/>
         <v>9240</v>
       </c>
-      <c r="V19" s="31">
+      <c r="V19" s="34">
         <f t="shared" si="2"/>
         <v>36960</v>
       </c>
@@ -3090,69 +3103,69 @@
       <c r="A20" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="B20" s="32">
+      <c r="B20" s="33">
         <v>46147</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="D20" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="34">
         <v>24</v>
       </c>
-      <c r="F20" s="31" t="s">
+      <c r="F20" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="G20" s="31" t="s">
+      <c r="G20" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H20" s="31" t="s">
+      <c r="H20" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I20" s="31" t="s">
+      <c r="I20" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J20" s="31" t="s">
+      <c r="J20" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="K20" s="31">
+      <c r="K20" s="34">
         <v>9</v>
       </c>
-      <c r="L20" s="31">
+      <c r="L20" s="34">
         <v>150</v>
       </c>
-      <c r="M20" s="31">
+      <c r="M20" s="34">
         <v>0.15</v>
       </c>
-      <c r="N20" s="31" t="s">
+      <c r="N20" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="O20" s="31" t="s">
+      <c r="O20" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P20" s="32">
+      <c r="P20" s="33">
         <v>46151</v>
       </c>
-      <c r="Q20" s="31">
+      <c r="Q20" s="34">
         <v>5</v>
       </c>
-      <c r="R20" s="31" t="s">
+      <c r="R20" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S20" s="31" t="s">
+      <c r="S20" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="T20" s="31">
+      <c r="T20" s="34">
         <f t="shared" si="0"/>
         <v>1350</v>
       </c>
-      <c r="U20" s="31">
+      <c r="U20" s="34">
         <f t="shared" si="1"/>
         <v>202.5</v>
       </c>
-      <c r="V20" s="31">
+      <c r="V20" s="34">
         <f t="shared" si="2"/>
         <v>1147.5</v>
       </c>
@@ -3161,69 +3174,69 @@
       <c r="A21" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="B21" s="32">
+      <c r="B21" s="33">
         <v>46071</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C21" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="D21" s="31" t="s">
+      <c r="D21" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="34">
         <v>58</v>
       </c>
-      <c r="F21" s="31" t="s">
+      <c r="F21" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="G21" s="31" t="s">
+      <c r="G21" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="H21" s="31" t="s">
+      <c r="H21" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I21" s="31" t="s">
+      <c r="I21" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="J21" s="31" t="s">
+      <c r="J21" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="K21" s="31">
+      <c r="K21" s="34">
         <v>11</v>
       </c>
-      <c r="L21" s="31">
+      <c r="L21" s="34">
         <v>2200</v>
       </c>
-      <c r="M21" s="31">
+      <c r="M21" s="34">
         <v>0</v>
       </c>
-      <c r="N21" s="31" t="s">
+      <c r="N21" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O21" s="31" t="s">
+      <c r="O21" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P21" s="32">
+      <c r="P21" s="33">
         <v>46074</v>
       </c>
-      <c r="Q21" s="31">
+      <c r="Q21" s="34">
         <v>5</v>
       </c>
-      <c r="R21" s="31" t="s">
+      <c r="R21" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S21" s="31" t="s">
+      <c r="S21" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="T21" s="31">
+      <c r="T21" s="34">
         <f t="shared" si="0"/>
         <v>24200</v>
       </c>
-      <c r="U21" s="31">
+      <c r="U21" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V21" s="31">
+      <c r="V21" s="34">
         <f t="shared" si="2"/>
         <v>24200</v>
       </c>
@@ -3232,69 +3245,69 @@
       <c r="A22" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="B22" s="32">
+      <c r="B22" s="33">
         <v>46153</v>
       </c>
-      <c r="C22" s="31" t="s">
+      <c r="C22" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="D22" s="31" t="s">
+      <c r="D22" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="34">
         <v>59</v>
       </c>
-      <c r="F22" s="31" t="s">
+      <c r="F22" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="G22" s="31" t="s">
+      <c r="G22" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H22" s="31" t="s">
+      <c r="H22" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I22" s="31" t="s">
+      <c r="I22" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="J22" s="31" t="s">
+      <c r="J22" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="K22" s="31">
+      <c r="K22" s="34">
         <v>4</v>
       </c>
-      <c r="L22" s="31">
+      <c r="L22" s="34">
         <v>3500</v>
       </c>
-      <c r="M22" s="31">
+      <c r="M22" s="34">
         <v>0.2</v>
       </c>
-      <c r="N22" s="31" t="s">
+      <c r="N22" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O22" s="31" t="s">
+      <c r="O22" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P22" s="32">
+      <c r="P22" s="33">
         <v>46154</v>
       </c>
-      <c r="Q22" s="31">
+      <c r="Q22" s="34">
         <v>1</v>
       </c>
-      <c r="R22" s="31" t="s">
+      <c r="R22" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S22" s="31" t="s">
+      <c r="S22" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="T22" s="31">
+      <c r="T22" s="34">
         <f t="shared" si="0"/>
         <v>14000</v>
       </c>
-      <c r="U22" s="31">
+      <c r="U22" s="34">
         <f t="shared" si="1"/>
         <v>2800</v>
       </c>
-      <c r="V22" s="31">
+      <c r="V22" s="34">
         <f t="shared" si="2"/>
         <v>11200</v>
       </c>
@@ -3303,69 +3316,69 @@
       <c r="A23" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="B23" s="32">
+      <c r="B23" s="33">
         <v>46191</v>
       </c>
-      <c r="C23" s="31" t="s">
+      <c r="C23" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="D23" s="31" t="s">
+      <c r="D23" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E23" s="31">
+      <c r="E23" s="34">
         <v>37</v>
       </c>
-      <c r="F23" s="31" t="s">
+      <c r="F23" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="G23" s="31" t="s">
+      <c r="G23" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H23" s="31" t="s">
+      <c r="H23" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I23" s="31" t="s">
+      <c r="I23" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="J23" s="31" t="s">
+      <c r="J23" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="K23" s="31">
+      <c r="K23" s="34">
         <v>9</v>
       </c>
-      <c r="L23" s="31">
+      <c r="L23" s="34">
         <v>750</v>
       </c>
-      <c r="M23" s="31">
+      <c r="M23" s="34">
         <v>0.15</v>
       </c>
-      <c r="N23" s="31" t="s">
+      <c r="N23" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O23" s="31" t="s">
+      <c r="O23" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P23" s="32">
+      <c r="P23" s="33">
         <v>46196</v>
       </c>
-      <c r="Q23" s="31">
+      <c r="Q23" s="34">
         <v>3</v>
       </c>
-      <c r="R23" s="31" t="s">
+      <c r="R23" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S23" s="31" t="s">
+      <c r="S23" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="T23" s="31">
+      <c r="T23" s="34">
         <f t="shared" si="0"/>
         <v>6750</v>
       </c>
-      <c r="U23" s="31">
+      <c r="U23" s="34">
         <f t="shared" si="1"/>
         <v>1012.5</v>
       </c>
-      <c r="V23" s="31">
+      <c r="V23" s="34">
         <f t="shared" si="2"/>
         <v>5737.5</v>
       </c>
@@ -3374,69 +3387,69 @@
       <c r="A24" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="B24" s="32">
+      <c r="B24" s="33">
         <v>46260</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="31" t="s">
+      <c r="D24" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="34">
         <v>50</v>
       </c>
-      <c r="F24" s="31" t="s">
+      <c r="F24" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="G24" s="31" t="s">
+      <c r="G24" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="H24" s="31" t="s">
+      <c r="H24" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I24" s="31" t="s">
+      <c r="I24" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="J24" s="31" t="s">
+      <c r="J24" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="K24" s="31">
+      <c r="K24" s="34">
         <v>18</v>
       </c>
-      <c r="L24" s="31">
+      <c r="L24" s="34">
         <v>2200</v>
       </c>
-      <c r="M24" s="31">
+      <c r="M24" s="34">
         <v>0.05</v>
       </c>
-      <c r="N24" s="31" t="s">
+      <c r="N24" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="O24" s="31" t="s">
+      <c r="O24" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P24" s="32">
+      <c r="P24" s="33">
         <v>46267</v>
       </c>
-      <c r="Q24" s="31">
+      <c r="Q24" s="34">
         <v>3</v>
       </c>
-      <c r="R24" s="31" t="s">
+      <c r="R24" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S24" s="31" t="s">
+      <c r="S24" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="T24" s="31">
+      <c r="T24" s="34">
         <f t="shared" si="0"/>
         <v>39600</v>
       </c>
-      <c r="U24" s="31">
+      <c r="U24" s="34">
         <f t="shared" si="1"/>
         <v>1980</v>
       </c>
-      <c r="V24" s="31">
+      <c r="V24" s="34">
         <f t="shared" si="2"/>
         <v>37620</v>
       </c>
@@ -3445,69 +3458,69 @@
       <c r="A25" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="B25" s="32">
+      <c r="B25" s="33">
         <v>46117</v>
       </c>
-      <c r="C25" s="31" t="s">
+      <c r="C25" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="D25" s="31" t="s">
+      <c r="D25" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="34">
         <v>55</v>
       </c>
-      <c r="F25" s="31" t="s">
+      <c r="F25" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="G25" s="31" t="s">
+      <c r="G25" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="H25" s="31" t="s">
+      <c r="H25" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I25" s="31" t="s">
+      <c r="I25" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="J25" s="31" t="s">
+      <c r="J25" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="K25" s="31">
+      <c r="K25" s="34">
         <v>21</v>
       </c>
-      <c r="L25" s="31">
+      <c r="L25" s="34">
         <v>320</v>
       </c>
-      <c r="M25" s="31">
+      <c r="M25" s="34">
         <v>0.2</v>
       </c>
-      <c r="N25" s="31" t="s">
+      <c r="N25" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O25" s="31" t="s">
+      <c r="O25" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P25" s="32">
+      <c r="P25" s="33">
         <v>46120</v>
       </c>
-      <c r="Q25" s="31">
+      <c r="Q25" s="34">
         <v>5</v>
       </c>
-      <c r="R25" s="31" t="s">
+      <c r="R25" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S25" s="31" t="s">
+      <c r="S25" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="T25" s="31">
+      <c r="T25" s="34">
         <f t="shared" si="0"/>
         <v>6720</v>
       </c>
-      <c r="U25" s="31">
+      <c r="U25" s="34">
         <f t="shared" si="1"/>
         <v>1344</v>
       </c>
-      <c r="V25" s="31">
+      <c r="V25" s="34">
         <f t="shared" si="2"/>
         <v>5376</v>
       </c>
@@ -3516,69 +3529,69 @@
       <c r="A26" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="B26" s="32">
+      <c r="B26" s="33">
         <v>46049</v>
       </c>
-      <c r="C26" s="31" t="s">
+      <c r="C26" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="D26" s="31" t="s">
+      <c r="D26" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E26" s="31">
+      <c r="E26" s="34">
         <v>27</v>
       </c>
-      <c r="F26" s="31" t="s">
+      <c r="F26" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="G26" s="31" t="s">
+      <c r="G26" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="H26" s="31" t="s">
+      <c r="H26" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I26" s="31" t="s">
+      <c r="I26" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="J26" s="31" t="s">
+      <c r="J26" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="K26" s="31">
+      <c r="K26" s="34">
         <v>10</v>
       </c>
-      <c r="L26" s="31">
+      <c r="L26" s="34">
         <v>3500</v>
       </c>
-      <c r="M26" s="31">
+      <c r="M26" s="34">
         <v>0.2</v>
       </c>
-      <c r="N26" s="31" t="s">
+      <c r="N26" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O26" s="31" t="s">
+      <c r="O26" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="P26" s="32">
+      <c r="P26" s="33">
         <v>46051</v>
       </c>
-      <c r="Q26" s="31">
+      <c r="Q26" s="34">
         <v>2</v>
       </c>
-      <c r="R26" s="31" t="s">
+      <c r="R26" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S26" s="31" t="s">
+      <c r="S26" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="T26" s="31">
+      <c r="T26" s="34">
         <f t="shared" si="0"/>
         <v>35000</v>
       </c>
-      <c r="U26" s="31">
+      <c r="U26" s="34">
         <f t="shared" si="1"/>
         <v>7000</v>
       </c>
-      <c r="V26" s="31">
+      <c r="V26" s="34">
         <f t="shared" si="2"/>
         <v>28000</v>
       </c>
@@ -3587,69 +3600,69 @@
       <c r="A27" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="B27" s="32">
+      <c r="B27" s="33">
         <v>46148</v>
       </c>
-      <c r="C27" s="31" t="s">
+      <c r="C27" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="D27" s="31" t="s">
+      <c r="D27" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="34">
         <v>61</v>
       </c>
-      <c r="F27" s="31" t="s">
+      <c r="F27" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="G27" s="31" t="s">
+      <c r="G27" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H27" s="31" t="s">
+      <c r="H27" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I27" s="31" t="s">
+      <c r="I27" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J27" s="31" t="s">
+      <c r="J27" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="K27" s="31">
+      <c r="K27" s="34">
         <v>11</v>
       </c>
-      <c r="L27" s="31">
+      <c r="L27" s="34">
         <v>150</v>
       </c>
-      <c r="M27" s="31">
+      <c r="M27" s="34">
         <v>0.05</v>
       </c>
-      <c r="N27" s="31" t="s">
+      <c r="N27" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="O27" s="31" t="s">
+      <c r="O27" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P27" s="32">
+      <c r="P27" s="33">
         <v>46151</v>
       </c>
-      <c r="Q27" s="31">
+      <c r="Q27" s="34">
         <v>4</v>
       </c>
-      <c r="R27" s="31" t="s">
+      <c r="R27" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S27" s="31" t="s">
+      <c r="S27" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="T27" s="31">
+      <c r="T27" s="34">
         <f t="shared" si="0"/>
         <v>1650</v>
       </c>
-      <c r="U27" s="31">
+      <c r="U27" s="34">
         <f t="shared" si="1"/>
         <v>82.5</v>
       </c>
-      <c r="V27" s="31">
+      <c r="V27" s="34">
         <f t="shared" si="2"/>
         <v>1567.5</v>
       </c>
@@ -3658,69 +3671,69 @@
       <c r="A28" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="B28" s="32">
+      <c r="B28" s="33">
         <v>46025</v>
       </c>
-      <c r="C28" s="31" t="s">
+      <c r="C28" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="D28" s="31" t="s">
+      <c r="D28" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E28" s="31">
+      <c r="E28" s="34">
         <v>55</v>
       </c>
-      <c r="F28" s="31" t="s">
+      <c r="F28" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="G28" s="31" t="s">
+      <c r="G28" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H28" s="31" t="s">
+      <c r="H28" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I28" s="31" t="s">
+      <c r="I28" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="J28" s="31" t="s">
+      <c r="J28" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="K28" s="31">
+      <c r="K28" s="34">
         <v>5</v>
       </c>
-      <c r="L28" s="31">
+      <c r="L28" s="34">
         <v>320</v>
       </c>
-      <c r="M28" s="31">
+      <c r="M28" s="34">
         <v>0.15</v>
       </c>
-      <c r="N28" s="31" t="s">
+      <c r="N28" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O28" s="31" t="s">
+      <c r="O28" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P28" s="32">
+      <c r="P28" s="33">
         <v>46026</v>
       </c>
-      <c r="Q28" s="31">
+      <c r="Q28" s="34">
         <v>3</v>
       </c>
-      <c r="R28" s="31" t="s">
+      <c r="R28" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S28" s="31" t="s">
+      <c r="S28" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="T28" s="31">
+      <c r="T28" s="34">
         <f t="shared" si="0"/>
         <v>1600</v>
       </c>
-      <c r="U28" s="31">
+      <c r="U28" s="34">
         <f t="shared" si="1"/>
         <v>240</v>
       </c>
-      <c r="V28" s="31">
+      <c r="V28" s="34">
         <f t="shared" si="2"/>
         <v>1360</v>
       </c>
@@ -3729,69 +3742,69 @@
       <c r="A29" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="B29" s="32">
+      <c r="B29" s="33">
         <v>46076</v>
       </c>
-      <c r="C29" s="31" t="s">
+      <c r="C29" s="35" t="s">
         <v>145</v>
       </c>
-      <c r="D29" s="31" t="s">
+      <c r="D29" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E29" s="31">
+      <c r="E29" s="34">
         <v>43</v>
       </c>
-      <c r="F29" s="31" t="s">
+      <c r="F29" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="G29" s="31" t="s">
+      <c r="G29" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="H29" s="31" t="s">
+      <c r="H29" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I29" s="31" t="s">
+      <c r="I29" s="35" t="s">
         <v>146</v>
       </c>
-      <c r="J29" s="31" t="s">
+      <c r="J29" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="K29" s="31">
+      <c r="K29" s="34">
         <v>24</v>
       </c>
-      <c r="L29" s="31">
+      <c r="L29" s="34">
         <v>1800</v>
       </c>
-      <c r="M29" s="31">
+      <c r="M29" s="34">
         <v>0.05</v>
       </c>
-      <c r="N29" s="31" t="s">
+      <c r="N29" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O29" s="31" t="s">
+      <c r="O29" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="P29" s="32">
+      <c r="P29" s="33">
         <v>46082</v>
       </c>
-      <c r="Q29" s="31">
+      <c r="Q29" s="34">
         <v>2</v>
       </c>
-      <c r="R29" s="31" t="s">
+      <c r="R29" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S29" s="31" t="s">
+      <c r="S29" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="T29" s="31">
+      <c r="T29" s="34">
         <f t="shared" si="0"/>
         <v>43200</v>
       </c>
-      <c r="U29" s="31">
+      <c r="U29" s="34">
         <f t="shared" si="1"/>
         <v>2160</v>
       </c>
-      <c r="V29" s="31">
+      <c r="V29" s="34">
         <f t="shared" si="2"/>
         <v>41040</v>
       </c>
@@ -3800,69 +3813,69 @@
       <c r="A30" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="B30" s="32">
+      <c r="B30" s="33">
         <v>46068</v>
       </c>
-      <c r="C30" s="31" t="s">
+      <c r="C30" s="35" t="s">
         <v>148</v>
       </c>
-      <c r="D30" s="31" t="s">
+      <c r="D30" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E30" s="31">
+      <c r="E30" s="34">
         <v>36</v>
       </c>
-      <c r="F30" s="31" t="s">
+      <c r="F30" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="G30" s="31" t="s">
+      <c r="G30" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H30" s="31" t="s">
+      <c r="H30" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I30" s="31" t="s">
+      <c r="I30" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="J30" s="31" t="s">
+      <c r="J30" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="K30" s="31">
+      <c r="K30" s="34">
         <v>2</v>
       </c>
-      <c r="L30" s="31">
+      <c r="L30" s="34">
         <v>55000</v>
       </c>
-      <c r="M30" s="31">
+      <c r="M30" s="34">
         <v>0.15</v>
       </c>
-      <c r="N30" s="31" t="s">
+      <c r="N30" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O30" s="31" t="s">
+      <c r="O30" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P30" s="32">
+      <c r="P30" s="33">
         <v>46074</v>
       </c>
-      <c r="Q30" s="31">
+      <c r="Q30" s="34">
         <v>4</v>
       </c>
-      <c r="R30" s="31" t="s">
+      <c r="R30" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S30" s="31" t="s">
+      <c r="S30" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="T30" s="31">
+      <c r="T30" s="34">
         <f t="shared" si="0"/>
         <v>110000</v>
       </c>
-      <c r="U30" s="31">
+      <c r="U30" s="34">
         <f t="shared" si="1"/>
         <v>16500</v>
       </c>
-      <c r="V30" s="31">
+      <c r="V30" s="34">
         <f t="shared" si="2"/>
         <v>93500</v>
       </c>
@@ -3871,69 +3884,69 @@
       <c r="A31" s="31" t="s">
         <v>149</v>
       </c>
-      <c r="B31" s="32">
+      <c r="B31" s="33">
         <v>46233</v>
       </c>
-      <c r="C31" s="31" t="s">
+      <c r="C31" s="35" t="s">
         <v>145</v>
       </c>
-      <c r="D31" s="31" t="s">
+      <c r="D31" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E31" s="31">
+      <c r="E31" s="34">
         <v>22</v>
       </c>
-      <c r="F31" s="31" t="s">
+      <c r="F31" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="G31" s="31" t="s">
+      <c r="G31" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="H31" s="31" t="s">
+      <c r="H31" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I31" s="31" t="s">
+      <c r="I31" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="J31" s="31" t="s">
+      <c r="J31" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="K31" s="31">
+      <c r="K31" s="34">
         <v>9</v>
       </c>
-      <c r="L31" s="31">
+      <c r="L31" s="34">
         <v>14500</v>
       </c>
-      <c r="M31" s="31">
+      <c r="M31" s="34">
         <v>0</v>
       </c>
-      <c r="N31" s="31" t="s">
+      <c r="N31" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="O31" s="31" t="s">
+      <c r="O31" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P31" s="32">
+      <c r="P31" s="33">
         <v>46240</v>
       </c>
-      <c r="Q31" s="31">
+      <c r="Q31" s="34">
         <v>5</v>
       </c>
-      <c r="R31" s="31" t="s">
+      <c r="R31" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S31" s="31" t="s">
+      <c r="S31" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="T31" s="31">
+      <c r="T31" s="34">
         <f t="shared" si="0"/>
         <v>130500</v>
       </c>
-      <c r="U31" s="31">
+      <c r="U31" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V31" s="31">
+      <c r="V31" s="34">
         <f t="shared" si="2"/>
         <v>130500</v>
       </c>
@@ -3942,69 +3955,69 @@
       <c r="A32" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="B32" s="32">
+      <c r="B32" s="33">
         <v>46238</v>
       </c>
-      <c r="C32" s="31" t="s">
+      <c r="C32" s="35" t="s">
         <v>148</v>
       </c>
-      <c r="D32" s="31" t="s">
+      <c r="D32" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E32" s="31">
+      <c r="E32" s="34">
         <v>28</v>
       </c>
-      <c r="F32" s="31" t="s">
+      <c r="F32" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="G32" s="31" t="s">
+      <c r="G32" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H32" s="31" t="s">
+      <c r="H32" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I32" s="31" t="s">
+      <c r="I32" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="J32" s="31" t="s">
+      <c r="J32" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="K32" s="31">
+      <c r="K32" s="34">
         <v>2</v>
       </c>
-      <c r="L32" s="31">
+      <c r="L32" s="34">
         <v>12500</v>
       </c>
-      <c r="M32" s="31">
+      <c r="M32" s="34">
         <v>0</v>
       </c>
-      <c r="N32" s="31" t="s">
+      <c r="N32" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="O32" s="31" t="s">
+      <c r="O32" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P32" s="32">
+      <c r="P32" s="33">
         <v>46243</v>
       </c>
-      <c r="Q32" s="31">
+      <c r="Q32" s="34">
         <v>3</v>
       </c>
-      <c r="R32" s="31" t="s">
+      <c r="R32" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S32" s="31" t="s">
+      <c r="S32" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="T32" s="31">
+      <c r="T32" s="34">
         <f t="shared" si="0"/>
         <v>25000</v>
       </c>
-      <c r="U32" s="31">
+      <c r="U32" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V32" s="31">
+      <c r="V32" s="34">
         <f t="shared" si="2"/>
         <v>25000</v>
       </c>
@@ -4013,69 +4026,69 @@
       <c r="A33" s="31" t="s">
         <v>152</v>
       </c>
-      <c r="B33" s="32">
+      <c r="B33" s="33">
         <v>46153</v>
       </c>
-      <c r="C33" s="31" t="s">
+      <c r="C33" s="35" t="s">
         <v>153</v>
       </c>
-      <c r="D33" s="31" t="s">
+      <c r="D33" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E33" s="31">
+      <c r="E33" s="34">
         <v>37</v>
       </c>
-      <c r="F33" s="31" t="s">
+      <c r="F33" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="G33" s="31" t="s">
+      <c r="G33" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H33" s="31" t="s">
+      <c r="H33" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I33" s="31" t="s">
+      <c r="I33" s="35" t="s">
         <v>146</v>
       </c>
-      <c r="J33" s="31" t="s">
+      <c r="J33" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="K33" s="31">
+      <c r="K33" s="34">
         <v>17</v>
       </c>
-      <c r="L33" s="31">
+      <c r="L33" s="34">
         <v>1800</v>
       </c>
-      <c r="M33" s="31">
+      <c r="M33" s="34">
         <v>0.2</v>
       </c>
-      <c r="N33" s="31" t="s">
+      <c r="N33" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O33" s="31" t="s">
+      <c r="O33" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P33" s="32">
+      <c r="P33" s="33">
         <v>46154</v>
       </c>
-      <c r="Q33" s="31">
+      <c r="Q33" s="34">
         <v>1</v>
       </c>
-      <c r="R33" s="31" t="s">
+      <c r="R33" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S33" s="31" t="s">
+      <c r="S33" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="T33" s="31">
+      <c r="T33" s="34">
         <f t="shared" si="0"/>
         <v>30600</v>
       </c>
-      <c r="U33" s="31">
+      <c r="U33" s="34">
         <f t="shared" si="1"/>
         <v>6120</v>
       </c>
-      <c r="V33" s="31">
+      <c r="V33" s="34">
         <f t="shared" si="2"/>
         <v>24480</v>
       </c>
@@ -4084,69 +4097,69 @@
       <c r="A34" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="B34" s="32">
+      <c r="B34" s="33">
         <v>46103</v>
       </c>
-      <c r="C34" s="31" t="s">
+      <c r="C34" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D34" s="31" t="s">
+      <c r="D34" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E34" s="31">
+      <c r="E34" s="34">
         <v>53</v>
       </c>
-      <c r="F34" s="31" t="s">
+      <c r="F34" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="G34" s="31" t="s">
+      <c r="G34" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H34" s="31" t="s">
+      <c r="H34" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I34" s="31" t="s">
+      <c r="I34" s="35" t="s">
         <v>146</v>
       </c>
-      <c r="J34" s="31" t="s">
+      <c r="J34" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="K34" s="31">
+      <c r="K34" s="34">
         <v>13</v>
       </c>
-      <c r="L34" s="31">
+      <c r="L34" s="34">
         <v>1800</v>
       </c>
-      <c r="M34" s="31">
+      <c r="M34" s="34">
         <v>0.25</v>
       </c>
-      <c r="N34" s="31" t="s">
+      <c r="N34" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="O34" s="31" t="s">
+      <c r="O34" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P34" s="32">
+      <c r="P34" s="33">
         <v>46109</v>
       </c>
-      <c r="Q34" s="31">
+      <c r="Q34" s="34">
         <v>2</v>
       </c>
-      <c r="R34" s="31" t="s">
+      <c r="R34" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S34" s="31" t="s">
+      <c r="S34" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="T34" s="31">
+      <c r="T34" s="34">
         <f t="shared" ref="T34:T65" si="3">K34*L34</f>
         <v>23400</v>
       </c>
-      <c r="U34" s="31">
+      <c r="U34" s="34">
         <f t="shared" ref="U34:U65" si="4">T34*M34</f>
         <v>5850</v>
       </c>
-      <c r="V34" s="31">
+      <c r="V34" s="34">
         <f t="shared" ref="V34:V65" si="5">T34-U34</f>
         <v>17550</v>
       </c>
@@ -4155,69 +4168,69 @@
       <c r="A35" s="31" t="s">
         <v>156</v>
       </c>
-      <c r="B35" s="32">
+      <c r="B35" s="33">
         <v>46263</v>
       </c>
-      <c r="C35" s="31" t="s">
+      <c r="C35" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="D35" s="31" t="s">
+      <c r="D35" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E35" s="31">
+      <c r="E35" s="34">
         <v>60</v>
       </c>
-      <c r="F35" s="31" t="s">
+      <c r="F35" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="G35" s="31" t="s">
+      <c r="G35" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="H35" s="31" t="s">
+      <c r="H35" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I35" s="31" t="s">
+      <c r="I35" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="J35" s="31" t="s">
+      <c r="J35" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="K35" s="31">
+      <c r="K35" s="34">
         <v>1</v>
       </c>
-      <c r="L35" s="31">
+      <c r="L35" s="34">
         <v>450</v>
       </c>
-      <c r="M35" s="31">
+      <c r="M35" s="34">
         <v>0.1</v>
       </c>
-      <c r="N35" s="31" t="s">
+      <c r="N35" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="O35" s="31" t="s">
+      <c r="O35" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P35" s="32">
+      <c r="P35" s="33">
         <v>46267</v>
       </c>
-      <c r="Q35" s="31">
+      <c r="Q35" s="34">
         <v>5</v>
       </c>
-      <c r="R35" s="31" t="s">
+      <c r="R35" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S35" s="31" t="s">
+      <c r="S35" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="T35" s="31">
+      <c r="T35" s="34">
         <f t="shared" si="3"/>
         <v>450</v>
       </c>
-      <c r="U35" s="31">
+      <c r="U35" s="34">
         <f t="shared" si="4"/>
         <v>45</v>
       </c>
-      <c r="V35" s="31">
+      <c r="V35" s="34">
         <f t="shared" si="5"/>
         <v>405</v>
       </c>
@@ -4226,69 +4239,69 @@
       <c r="A36" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="B36" s="32">
+      <c r="B36" s="33">
         <v>46136</v>
       </c>
-      <c r="C36" s="31" t="s">
+      <c r="C36" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="D36" s="31" t="s">
+      <c r="D36" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E36" s="31">
+      <c r="E36" s="34">
         <v>53</v>
       </c>
-      <c r="F36" s="31" t="s">
+      <c r="F36" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="G36" s="31" t="s">
+      <c r="G36" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H36" s="31" t="s">
+      <c r="H36" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I36" s="31" t="s">
+      <c r="I36" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="J36" s="31" t="s">
+      <c r="J36" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="K36" s="31">
+      <c r="K36" s="34">
         <v>3</v>
       </c>
-      <c r="L36" s="31">
+      <c r="L36" s="34">
         <v>3500</v>
       </c>
-      <c r="M36" s="31">
+      <c r="M36" s="34">
         <v>0.1</v>
       </c>
-      <c r="N36" s="31" t="s">
+      <c r="N36" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="O36" s="31" t="s">
+      <c r="O36" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P36" s="32">
+      <c r="P36" s="33">
         <v>46140</v>
       </c>
-      <c r="Q36" s="31">
+      <c r="Q36" s="34">
         <v>5</v>
       </c>
-      <c r="R36" s="31" t="s">
+      <c r="R36" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S36" s="31" t="s">
+      <c r="S36" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="T36" s="31">
+      <c r="T36" s="34">
         <f t="shared" si="3"/>
         <v>10500</v>
       </c>
-      <c r="U36" s="31">
+      <c r="U36" s="34">
         <f t="shared" si="4"/>
         <v>1050</v>
       </c>
-      <c r="V36" s="31">
+      <c r="V36" s="34">
         <f t="shared" si="5"/>
         <v>9450</v>
       </c>
@@ -4297,69 +4310,69 @@
       <c r="A37" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="B37" s="32">
+      <c r="B37" s="33">
         <v>46232</v>
       </c>
-      <c r="C37" s="31" t="s">
+      <c r="C37" s="35" t="s">
         <v>145</v>
       </c>
-      <c r="D37" s="31" t="s">
+      <c r="D37" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E37" s="31">
+      <c r="E37" s="34">
         <v>35</v>
       </c>
-      <c r="F37" s="31" t="s">
+      <c r="F37" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="G37" s="31" t="s">
+      <c r="G37" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="H37" s="31" t="s">
+      <c r="H37" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I37" s="31" t="s">
+      <c r="I37" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="J37" s="31" t="s">
+      <c r="J37" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="K37" s="31">
+      <c r="K37" s="34">
         <v>2</v>
       </c>
-      <c r="L37" s="31">
+      <c r="L37" s="34">
         <v>1200</v>
       </c>
-      <c r="M37" s="31">
+      <c r="M37" s="34">
         <v>0.05</v>
       </c>
-      <c r="N37" s="31" t="s">
+      <c r="N37" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="O37" s="31" t="s">
+      <c r="O37" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P37" s="32">
+      <c r="P37" s="33">
         <v>46239</v>
       </c>
-      <c r="Q37" s="31">
+      <c r="Q37" s="34">
         <v>1</v>
       </c>
-      <c r="R37" s="31" t="s">
+      <c r="R37" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S37" s="31" t="s">
+      <c r="S37" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="T37" s="31">
+      <c r="T37" s="34">
         <f t="shared" si="3"/>
         <v>2400</v>
       </c>
-      <c r="U37" s="31">
+      <c r="U37" s="34">
         <f t="shared" si="4"/>
         <v>120</v>
       </c>
-      <c r="V37" s="31">
+      <c r="V37" s="34">
         <f t="shared" si="5"/>
         <v>2280</v>
       </c>
@@ -4368,69 +4381,69 @@
       <c r="A38" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="B38" s="32">
+      <c r="B38" s="33">
         <v>46249</v>
       </c>
-      <c r="C38" s="31" t="s">
+      <c r="C38" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="D38" s="31" t="s">
+      <c r="D38" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E38" s="31">
+      <c r="E38" s="34">
         <v>45</v>
       </c>
-      <c r="F38" s="31" t="s">
+      <c r="F38" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="G38" s="31" t="s">
+      <c r="G38" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H38" s="31" t="s">
+      <c r="H38" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I38" s="31" t="s">
+      <c r="I38" s="35" t="s">
         <v>160</v>
       </c>
-      <c r="J38" s="31" t="s">
+      <c r="J38" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="K38" s="31">
+      <c r="K38" s="34">
         <v>21</v>
       </c>
-      <c r="L38" s="31">
+      <c r="L38" s="34">
         <v>45</v>
       </c>
-      <c r="M38" s="31">
+      <c r="M38" s="34">
         <v>0.25</v>
       </c>
-      <c r="N38" s="31" t="s">
+      <c r="N38" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O38" s="31" t="s">
+      <c r="O38" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="P38" s="32">
+      <c r="P38" s="33">
         <v>46255</v>
       </c>
-      <c r="Q38" s="31">
+      <c r="Q38" s="34">
         <v>1</v>
       </c>
-      <c r="R38" s="31" t="s">
+      <c r="R38" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S38" s="31" t="s">
+      <c r="S38" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="T38" s="31">
+      <c r="T38" s="34">
         <f t="shared" si="3"/>
         <v>945</v>
       </c>
-      <c r="U38" s="31">
+      <c r="U38" s="34">
         <f t="shared" si="4"/>
         <v>236.25</v>
       </c>
-      <c r="V38" s="31">
+      <c r="V38" s="34">
         <f t="shared" si="5"/>
         <v>708.75</v>
       </c>
@@ -4439,69 +4452,69 @@
       <c r="A39" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="B39" s="32">
+      <c r="B39" s="33">
         <v>46068</v>
       </c>
-      <c r="C39" s="31" t="s">
+      <c r="C39" s="35" t="s">
         <v>162</v>
       </c>
-      <c r="D39" s="31" t="s">
+      <c r="D39" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E39" s="31">
+      <c r="E39" s="34">
         <v>24</v>
       </c>
-      <c r="F39" s="31" t="s">
+      <c r="F39" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="G39" s="31" t="s">
+      <c r="G39" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H39" s="31" t="s">
+      <c r="H39" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I39" s="31" t="s">
+      <c r="I39" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="J39" s="31" t="s">
+      <c r="J39" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="K39" s="31">
+      <c r="K39" s="34">
         <v>5</v>
       </c>
-      <c r="L39" s="31">
+      <c r="L39" s="34">
         <v>55000</v>
       </c>
-      <c r="M39" s="31">
+      <c r="M39" s="34">
         <v>0.15</v>
       </c>
-      <c r="N39" s="31" t="s">
+      <c r="N39" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="O39" s="31" t="s">
+      <c r="O39" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="P39" s="32">
+      <c r="P39" s="33">
         <v>46075</v>
       </c>
-      <c r="Q39" s="31">
+      <c r="Q39" s="34">
         <v>5</v>
       </c>
-      <c r="R39" s="31" t="s">
+      <c r="R39" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S39" s="31" t="s">
+      <c r="S39" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="T39" s="31">
+      <c r="T39" s="34">
         <f t="shared" si="3"/>
         <v>275000</v>
       </c>
-      <c r="U39" s="31">
+      <c r="U39" s="34">
         <f t="shared" si="4"/>
         <v>41250</v>
       </c>
-      <c r="V39" s="31">
+      <c r="V39" s="34">
         <f t="shared" si="5"/>
         <v>233750</v>
       </c>
@@ -4510,69 +4523,69 @@
       <c r="A40" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="B40" s="32">
+      <c r="B40" s="33">
         <v>46251</v>
       </c>
-      <c r="C40" s="31" t="s">
+      <c r="C40" s="35" t="s">
         <v>164</v>
       </c>
-      <c r="D40" s="31" t="s">
+      <c r="D40" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E40" s="31">
+      <c r="E40" s="34">
         <v>56</v>
       </c>
-      <c r="F40" s="31" t="s">
+      <c r="F40" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="G40" s="31" t="s">
+      <c r="G40" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H40" s="31" t="s">
+      <c r="H40" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I40" s="31" t="s">
+      <c r="I40" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="J40" s="31" t="s">
+      <c r="J40" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="K40" s="31">
+      <c r="K40" s="34">
         <v>9</v>
       </c>
-      <c r="L40" s="31">
+      <c r="L40" s="34">
         <v>14500</v>
       </c>
-      <c r="M40" s="31">
+      <c r="M40" s="34">
         <v>0.05</v>
       </c>
-      <c r="N40" s="31" t="s">
+      <c r="N40" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="O40" s="31" t="s">
+      <c r="O40" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="P40" s="32">
+      <c r="P40" s="33">
         <v>46255</v>
       </c>
-      <c r="Q40" s="31">
+      <c r="Q40" s="34">
         <v>5</v>
       </c>
-      <c r="R40" s="31" t="s">
+      <c r="R40" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S40" s="31" t="s">
+      <c r="S40" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="T40" s="31">
+      <c r="T40" s="34">
         <f t="shared" si="3"/>
         <v>130500</v>
       </c>
-      <c r="U40" s="31">
+      <c r="U40" s="34">
         <f t="shared" si="4"/>
         <v>6525</v>
       </c>
-      <c r="V40" s="31">
+      <c r="V40" s="34">
         <f t="shared" si="5"/>
         <v>123975</v>
       </c>
@@ -4581,69 +4594,69 @@
       <c r="A41" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="B41" s="32">
+      <c r="B41" s="33">
         <v>46084</v>
       </c>
-      <c r="C41" s="31" t="s">
+      <c r="C41" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="D41" s="31" t="s">
+      <c r="D41" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E41" s="31">
+      <c r="E41" s="34">
         <v>39</v>
       </c>
-      <c r="F41" s="31" t="s">
+      <c r="F41" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="G41" s="31" t="s">
+      <c r="G41" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H41" s="31" t="s">
+      <c r="H41" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I41" s="31" t="s">
+      <c r="I41" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="J41" s="31" t="s">
+      <c r="J41" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="K41" s="31">
+      <c r="K41" s="34">
         <v>18</v>
       </c>
-      <c r="L41" s="31">
+      <c r="L41" s="34">
         <v>85</v>
       </c>
-      <c r="M41" s="31">
+      <c r="M41" s="34">
         <v>0</v>
       </c>
-      <c r="N41" s="31" t="s">
+      <c r="N41" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O41" s="31" t="s">
+      <c r="O41" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P41" s="32">
+      <c r="P41" s="33">
         <v>46087</v>
       </c>
-      <c r="Q41" s="31">
+      <c r="Q41" s="34">
         <v>4</v>
       </c>
-      <c r="R41" s="31" t="s">
+      <c r="R41" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S41" s="31" t="s">
+      <c r="S41" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="T41" s="31">
+      <c r="T41" s="34">
         <f t="shared" si="3"/>
         <v>1530</v>
       </c>
-      <c r="U41" s="31">
+      <c r="U41" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V41" s="31">
+      <c r="V41" s="34">
         <f t="shared" si="5"/>
         <v>1530</v>
       </c>
@@ -4652,69 +4665,69 @@
       <c r="A42" s="31" t="s">
         <v>166</v>
       </c>
-      <c r="B42" s="32">
+      <c r="B42" s="33">
         <v>46077</v>
       </c>
-      <c r="C42" s="31" t="s">
+      <c r="C42" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="D42" s="31" t="s">
+      <c r="D42" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E42" s="31">
+      <c r="E42" s="34">
         <v>42</v>
       </c>
-      <c r="F42" s="31" t="s">
+      <c r="F42" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="G42" s="31" t="s">
+      <c r="G42" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H42" s="31" t="s">
+      <c r="H42" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I42" s="31" t="s">
+      <c r="I42" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="J42" s="31" t="s">
+      <c r="J42" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="K42" s="31">
+      <c r="K42" s="34">
         <v>7</v>
       </c>
-      <c r="L42" s="31">
+      <c r="L42" s="34">
         <v>450</v>
       </c>
-      <c r="M42" s="31">
+      <c r="M42" s="34">
         <v>0.15</v>
       </c>
-      <c r="N42" s="31" t="s">
+      <c r="N42" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="O42" s="31" t="s">
+      <c r="O42" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="P42" s="32">
+      <c r="P42" s="33">
         <v>46078</v>
       </c>
-      <c r="Q42" s="31">
+      <c r="Q42" s="34">
         <v>5</v>
       </c>
-      <c r="R42" s="31" t="s">
+      <c r="R42" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S42" s="31" t="s">
+      <c r="S42" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="T42" s="31">
+      <c r="T42" s="34">
         <f t="shared" si="3"/>
         <v>3150</v>
       </c>
-      <c r="U42" s="31">
+      <c r="U42" s="34">
         <f t="shared" si="4"/>
         <v>472.5</v>
       </c>
-      <c r="V42" s="31">
+      <c r="V42" s="34">
         <f t="shared" si="5"/>
         <v>2677.5</v>
       </c>
@@ -4723,67 +4736,67 @@
       <c r="A43" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="B43" s="32">
+      <c r="B43" s="33">
         <v>46248</v>
       </c>
-      <c r="C43" s="31" t="s">
+      <c r="C43" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="D43" s="31" t="s">
+      <c r="D43" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E43" s="31">
+      <c r="E43" s="34">
         <v>51</v>
       </c>
-      <c r="F43" s="31" t="s">
+      <c r="F43" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="G43" s="31" t="s">
+      <c r="G43" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H43" s="31" t="s">
+      <c r="H43" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I43" s="31" t="s">
+      <c r="I43" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="J43" s="31" t="s">
+      <c r="J43" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="K43" s="31">
+      <c r="K43" s="34">
         <v>13</v>
       </c>
-      <c r="L43" s="31">
+      <c r="L43" s="34">
         <v>85</v>
       </c>
-      <c r="M43" s="31">
+      <c r="M43" s="34">
         <v>0.15</v>
       </c>
-      <c r="N43" s="31" t="s">
+      <c r="N43" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="O43" s="31" t="s">
+      <c r="O43" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="P43" s="32">
+      <c r="P43" s="33">
         <v>46255</v>
       </c>
-      <c r="Q43" s="31">
+      <c r="Q43" s="34">
         <v>5</v>
       </c>
-      <c r="R43" s="31" t="s">
+      <c r="R43" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S43" s="31"/>
-      <c r="T43" s="31">
+      <c r="S43" s="35"/>
+      <c r="T43" s="34">
         <f t="shared" si="3"/>
         <v>1105</v>
       </c>
-      <c r="U43" s="31">
+      <c r="U43" s="34">
         <f t="shared" si="4"/>
         <v>165.75</v>
       </c>
-      <c r="V43" s="31">
+      <c r="V43" s="34">
         <f t="shared" si="5"/>
         <v>939.25</v>
       </c>
@@ -4792,69 +4805,69 @@
       <c r="A44" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="B44" s="32">
+      <c r="B44" s="33">
         <v>46079</v>
       </c>
-      <c r="C44" s="31" t="s">
+      <c r="C44" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="D44" s="31" t="s">
+      <c r="D44" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="34">
         <v>22</v>
       </c>
-      <c r="F44" s="31" t="s">
+      <c r="F44" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="G44" s="31" t="s">
+      <c r="G44" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H44" s="31" t="s">
+      <c r="H44" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I44" s="31" t="s">
+      <c r="I44" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="J44" s="31" t="s">
+      <c r="J44" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="K44" s="31">
+      <c r="K44" s="34">
         <v>6</v>
       </c>
-      <c r="L44" s="31">
+      <c r="L44" s="34">
         <v>450</v>
       </c>
-      <c r="M44" s="31">
+      <c r="M44" s="34">
         <v>0.15</v>
       </c>
-      <c r="N44" s="31" t="s">
+      <c r="N44" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O44" s="31" t="s">
+      <c r="O44" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="P44" s="32">
+      <c r="P44" s="33">
         <v>46082</v>
       </c>
-      <c r="Q44" s="31">
+      <c r="Q44" s="34">
         <v>5</v>
       </c>
-      <c r="R44" s="31" t="s">
+      <c r="R44" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S44" s="31" t="s">
+      <c r="S44" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="T44" s="31">
+      <c r="T44" s="34">
         <f t="shared" si="3"/>
         <v>2700</v>
       </c>
-      <c r="U44" s="31">
+      <c r="U44" s="34">
         <f t="shared" si="4"/>
         <v>405</v>
       </c>
-      <c r="V44" s="31">
+      <c r="V44" s="34">
         <f t="shared" si="5"/>
         <v>2295</v>
       </c>
@@ -4863,69 +4876,69 @@
       <c r="A45" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="B45" s="32">
+      <c r="B45" s="33">
         <v>46174</v>
       </c>
-      <c r="C45" s="31" t="s">
+      <c r="C45" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="D45" s="31" t="s">
+      <c r="D45" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E45" s="31">
+      <c r="E45" s="34">
         <v>26</v>
       </c>
-      <c r="F45" s="31" t="s">
+      <c r="F45" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="G45" s="31" t="s">
+      <c r="G45" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="H45" s="31" t="s">
+      <c r="H45" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I45" s="31" t="s">
+      <c r="I45" s="35" t="s">
         <v>160</v>
       </c>
-      <c r="J45" s="31" t="s">
+      <c r="J45" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="K45" s="31">
+      <c r="K45" s="34">
         <v>15</v>
       </c>
-      <c r="L45" s="31">
+      <c r="L45" s="34">
         <v>45</v>
       </c>
-      <c r="M45" s="31">
+      <c r="M45" s="34">
         <v>0.05</v>
       </c>
-      <c r="N45" s="31" t="s">
+      <c r="N45" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O45" s="31" t="s">
+      <c r="O45" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P45" s="32">
+      <c r="P45" s="33">
         <v>46179</v>
       </c>
-      <c r="Q45" s="31">
+      <c r="Q45" s="34">
         <v>3</v>
       </c>
-      <c r="R45" s="31" t="s">
+      <c r="R45" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S45" s="31" t="s">
+      <c r="S45" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="T45" s="31">
+      <c r="T45" s="34">
         <f t="shared" si="3"/>
         <v>675</v>
       </c>
-      <c r="U45" s="31">
+      <c r="U45" s="34">
         <f t="shared" si="4"/>
         <v>33.75</v>
       </c>
-      <c r="V45" s="31">
+      <c r="V45" s="34">
         <f t="shared" si="5"/>
         <v>641.25</v>
       </c>
@@ -4934,69 +4947,69 @@
       <c r="A46" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="B46" s="32">
+      <c r="B46" s="33">
         <v>46106</v>
       </c>
-      <c r="C46" s="31" t="s">
+      <c r="C46" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="D46" s="31" t="s">
+      <c r="D46" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E46" s="31">
+      <c r="E46" s="34">
         <v>38</v>
       </c>
-      <c r="F46" s="31" t="s">
+      <c r="F46" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="G46" s="31" t="s">
+      <c r="G46" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="H46" s="31" t="s">
+      <c r="H46" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I46" s="31" t="s">
+      <c r="I46" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="J46" s="31" t="s">
+      <c r="J46" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="K46" s="31">
+      <c r="K46" s="34">
         <v>3</v>
       </c>
-      <c r="L46" s="31">
+      <c r="L46" s="34">
         <v>85</v>
       </c>
-      <c r="M46" s="31">
+      <c r="M46" s="34">
         <v>0.15</v>
       </c>
-      <c r="N46" s="31" t="s">
+      <c r="N46" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O46" s="31" t="s">
+      <c r="O46" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="P46" s="32">
+      <c r="P46" s="33">
         <v>46109</v>
       </c>
-      <c r="Q46" s="31">
+      <c r="Q46" s="34">
         <v>1</v>
       </c>
-      <c r="R46" s="31" t="s">
+      <c r="R46" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S46" s="31" t="s">
+      <c r="S46" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="T46" s="31">
+      <c r="T46" s="34">
         <f t="shared" si="3"/>
         <v>255</v>
       </c>
-      <c r="U46" s="31">
+      <c r="U46" s="34">
         <f t="shared" si="4"/>
         <v>38.25</v>
       </c>
-      <c r="V46" s="31">
+      <c r="V46" s="34">
         <f t="shared" si="5"/>
         <v>216.75</v>
       </c>
@@ -5005,69 +5018,69 @@
       <c r="A47" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="B47" s="32">
+      <c r="B47" s="33">
         <v>46189</v>
       </c>
-      <c r="C47" s="31" t="s">
+      <c r="C47" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="D47" s="31" t="s">
+      <c r="D47" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E47" s="31">
+      <c r="E47" s="34">
         <v>22</v>
       </c>
-      <c r="F47" s="31" t="s">
+      <c r="F47" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="G47" s="31" t="s">
+      <c r="G47" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H47" s="31" t="s">
+      <c r="H47" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I47" s="31" t="s">
+      <c r="I47" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="J47" s="31" t="s">
+      <c r="J47" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="K47" s="31">
+      <c r="K47" s="34">
         <v>5</v>
       </c>
-      <c r="L47" s="31">
+      <c r="L47" s="34">
         <v>55000</v>
       </c>
-      <c r="M47" s="31">
+      <c r="M47" s="34">
         <v>0.05</v>
       </c>
-      <c r="N47" s="31" t="s">
+      <c r="N47" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O47" s="31" t="s">
+      <c r="O47" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P47" s="32">
+      <c r="P47" s="33">
         <v>46190</v>
       </c>
-      <c r="Q47" s="31">
+      <c r="Q47" s="34">
         <v>1</v>
       </c>
-      <c r="R47" s="31" t="s">
+      <c r="R47" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S47" s="31" t="s">
+      <c r="S47" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="T47" s="31">
+      <c r="T47" s="34">
         <f t="shared" si="3"/>
         <v>275000</v>
       </c>
-      <c r="U47" s="31">
+      <c r="U47" s="34">
         <f t="shared" si="4"/>
         <v>13750</v>
       </c>
-      <c r="V47" s="31">
+      <c r="V47" s="34">
         <f t="shared" si="5"/>
         <v>261250</v>
       </c>
@@ -5076,69 +5089,69 @@
       <c r="A48" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="B48" s="32">
+      <c r="B48" s="33">
         <v>46202</v>
       </c>
-      <c r="C48" s="31" t="s">
+      <c r="C48" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="D48" s="31" t="s">
+      <c r="D48" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E48" s="31">
+      <c r="E48" s="34">
         <v>31</v>
       </c>
-      <c r="F48" s="31" t="s">
+      <c r="F48" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="G48" s="31" t="s">
+      <c r="G48" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="H48" s="31" t="s">
+      <c r="H48" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I48" s="31" t="s">
+      <c r="I48" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="J48" s="31" t="s">
+      <c r="J48" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="K48" s="31">
+      <c r="K48" s="34">
         <v>6</v>
       </c>
-      <c r="L48" s="31">
+      <c r="L48" s="34">
         <v>2200</v>
       </c>
-      <c r="M48" s="31">
+      <c r="M48" s="34">
         <v>0.1</v>
       </c>
-      <c r="N48" s="31" t="s">
+      <c r="N48" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O48" s="31" t="s">
+      <c r="O48" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P48" s="32">
+      <c r="P48" s="33">
         <v>46205</v>
       </c>
-      <c r="Q48" s="31">
+      <c r="Q48" s="34">
         <v>3</v>
       </c>
-      <c r="R48" s="31" t="s">
+      <c r="R48" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S48" s="31" t="s">
+      <c r="S48" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="T48" s="31">
+      <c r="T48" s="34">
         <f t="shared" si="3"/>
         <v>13200</v>
       </c>
-      <c r="U48" s="31">
+      <c r="U48" s="34">
         <f t="shared" si="4"/>
         <v>1320</v>
       </c>
-      <c r="V48" s="31">
+      <c r="V48" s="34">
         <f t="shared" si="5"/>
         <v>11880</v>
       </c>
@@ -5147,69 +5160,69 @@
       <c r="A49" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="B49" s="32">
+      <c r="B49" s="33">
         <v>46206</v>
       </c>
-      <c r="C49" s="31" t="s">
+      <c r="C49" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="D49" s="31" t="s">
+      <c r="D49" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E49" s="31">
+      <c r="E49" s="34">
         <v>27</v>
       </c>
-      <c r="F49" s="31" t="s">
+      <c r="F49" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="G49" s="31" t="s">
+      <c r="G49" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="H49" s="31" t="s">
+      <c r="H49" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I49" s="31" t="s">
+      <c r="I49" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="J49" s="31" t="s">
+      <c r="J49" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="K49" s="31">
+      <c r="K49" s="34">
         <v>4</v>
       </c>
-      <c r="L49" s="31">
+      <c r="L49" s="34">
         <v>320</v>
       </c>
-      <c r="M49" s="31">
+      <c r="M49" s="34">
         <v>0.2</v>
       </c>
-      <c r="N49" s="31" t="s">
+      <c r="N49" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O49" s="31" t="s">
+      <c r="O49" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P49" s="32">
+      <c r="P49" s="33">
         <v>46208</v>
       </c>
-      <c r="Q49" s="31">
+      <c r="Q49" s="34">
         <v>4</v>
       </c>
-      <c r="R49" s="31" t="s">
+      <c r="R49" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S49" s="31" t="s">
+      <c r="S49" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="T49" s="31">
+      <c r="T49" s="34">
         <f t="shared" si="3"/>
         <v>1280</v>
       </c>
-      <c r="U49" s="31">
+      <c r="U49" s="34">
         <f t="shared" si="4"/>
         <v>256</v>
       </c>
-      <c r="V49" s="31">
+      <c r="V49" s="34">
         <f t="shared" si="5"/>
         <v>1024</v>
       </c>
@@ -5218,69 +5231,69 @@
       <c r="A50" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="B50" s="32">
+      <c r="B50" s="33">
         <v>46152</v>
       </c>
-      <c r="C50" s="31" t="s">
+      <c r="C50" s="35" t="s">
         <v>148</v>
       </c>
-      <c r="D50" s="31" t="s">
+      <c r="D50" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E50" s="31">
+      <c r="E50" s="34">
         <v>47</v>
       </c>
-      <c r="F50" s="31" t="s">
+      <c r="F50" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="G50" s="31" t="s">
+      <c r="G50" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H50" s="31" t="s">
+      <c r="H50" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I50" s="31" t="s">
+      <c r="I50" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="J50" s="31" t="s">
+      <c r="J50" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="K50" s="31">
+      <c r="K50" s="34">
         <v>21</v>
       </c>
-      <c r="L50" s="31">
+      <c r="L50" s="34">
         <v>14500</v>
       </c>
-      <c r="M50" s="31">
+      <c r="M50" s="34">
         <v>0.15</v>
       </c>
-      <c r="N50" s="31" t="s">
+      <c r="N50" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O50" s="31" t="s">
+      <c r="O50" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P50" s="32">
+      <c r="P50" s="33">
         <v>46158</v>
       </c>
-      <c r="Q50" s="31">
+      <c r="Q50" s="34">
         <v>5</v>
       </c>
-      <c r="R50" s="31" t="s">
+      <c r="R50" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S50" s="31" t="s">
+      <c r="S50" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="T50" s="31">
+      <c r="T50" s="34">
         <f t="shared" si="3"/>
         <v>304500</v>
       </c>
-      <c r="U50" s="31">
+      <c r="U50" s="34">
         <f t="shared" si="4"/>
         <v>45675</v>
       </c>
-      <c r="V50" s="31">
+      <c r="V50" s="34">
         <f t="shared" si="5"/>
         <v>258825</v>
       </c>
@@ -5289,69 +5302,69 @@
       <c r="A51" s="31" t="s">
         <v>176</v>
       </c>
-      <c r="B51" s="32">
+      <c r="B51" s="33">
         <v>46229</v>
       </c>
-      <c r="C51" s="31" t="s">
+      <c r="C51" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="D51" s="31" t="s">
+      <c r="D51" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E51" s="31">
+      <c r="E51" s="34">
         <v>50</v>
       </c>
-      <c r="F51" s="31" t="s">
+      <c r="F51" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="G51" s="31" t="s">
+      <c r="G51" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H51" s="31" t="s">
+      <c r="H51" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I51" s="31" t="s">
+      <c r="I51" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="J51" s="31" t="s">
+      <c r="J51" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="K51" s="31">
+      <c r="K51" s="34">
         <v>11</v>
       </c>
-      <c r="L51" s="31">
+      <c r="L51" s="34">
         <v>250</v>
       </c>
-      <c r="M51" s="31">
+      <c r="M51" s="34">
         <v>0.05</v>
       </c>
-      <c r="N51" s="31" t="s">
+      <c r="N51" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O51" s="31" t="s">
+      <c r="O51" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P51" s="32">
+      <c r="P51" s="33">
         <v>46234</v>
       </c>
-      <c r="Q51" s="31">
+      <c r="Q51" s="34">
         <v>4</v>
       </c>
-      <c r="R51" s="31" t="s">
+      <c r="R51" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S51" s="31" t="s">
+      <c r="S51" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="T51" s="31">
+      <c r="T51" s="34">
         <f t="shared" si="3"/>
         <v>2750</v>
       </c>
-      <c r="U51" s="31">
+      <c r="U51" s="34">
         <f t="shared" si="4"/>
         <v>137.5</v>
       </c>
-      <c r="V51" s="31">
+      <c r="V51" s="34">
         <f t="shared" si="5"/>
         <v>2612.5</v>
       </c>
@@ -5360,69 +5373,69 @@
       <c r="A52" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="B52" s="32">
+      <c r="B52" s="33">
         <v>46141</v>
       </c>
-      <c r="C52" s="31" t="s">
+      <c r="C52" s="35" t="s">
         <v>164</v>
       </c>
-      <c r="D52" s="31" t="s">
+      <c r="D52" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E52" s="31">
+      <c r="E52" s="34">
         <v>42</v>
       </c>
-      <c r="F52" s="31" t="s">
+      <c r="F52" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="G52" s="31" t="s">
+      <c r="G52" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H52" s="31" t="s">
+      <c r="H52" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I52" s="31" t="s">
+      <c r="I52" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="J52" s="31" t="s">
+      <c r="J52" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="K52" s="31">
+      <c r="K52" s="34">
         <v>16</v>
       </c>
-      <c r="L52" s="31">
+      <c r="L52" s="34">
         <v>85</v>
       </c>
-      <c r="M52" s="31">
+      <c r="M52" s="34">
         <v>0.05</v>
       </c>
-      <c r="N52" s="31" t="s">
+      <c r="N52" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="O52" s="31" t="s">
+      <c r="O52" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="P52" s="32">
+      <c r="P52" s="33">
         <v>46146</v>
       </c>
-      <c r="Q52" s="31">
+      <c r="Q52" s="34">
         <v>3</v>
       </c>
-      <c r="R52" s="31" t="s">
+      <c r="R52" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S52" s="31" t="s">
+      <c r="S52" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="T52" s="31">
+      <c r="T52" s="34">
         <f t="shared" si="3"/>
         <v>1360</v>
       </c>
-      <c r="U52" s="31">
+      <c r="U52" s="34">
         <f t="shared" si="4"/>
         <v>68</v>
       </c>
-      <c r="V52" s="31">
+      <c r="V52" s="34">
         <f t="shared" si="5"/>
         <v>1292</v>
       </c>
@@ -5431,69 +5444,69 @@
       <c r="A53" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="B53" s="32">
+      <c r="B53" s="33">
         <v>46202</v>
       </c>
-      <c r="C53" s="31" t="s">
+      <c r="C53" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="D53" s="31" t="s">
+      <c r="D53" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E53" s="31">
+      <c r="E53" s="34">
         <v>54</v>
       </c>
-      <c r="F53" s="31" t="s">
+      <c r="F53" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="G53" s="31" t="s">
+      <c r="G53" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H53" s="31" t="s">
+      <c r="H53" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I53" s="31" t="s">
+      <c r="I53" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="J53" s="31" t="s">
+      <c r="J53" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="K53" s="31">
+      <c r="K53" s="34">
         <v>14</v>
       </c>
-      <c r="L53" s="31">
+      <c r="L53" s="34">
         <v>1200</v>
       </c>
-      <c r="M53" s="31">
+      <c r="M53" s="34">
         <v>0.15</v>
       </c>
-      <c r="N53" s="31" t="s">
+      <c r="N53" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="O53" s="31" t="s">
+      <c r="O53" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="P53" s="32">
+      <c r="P53" s="33">
         <v>46205</v>
       </c>
-      <c r="Q53" s="31">
+      <c r="Q53" s="34">
         <v>4</v>
       </c>
-      <c r="R53" s="31" t="s">
+      <c r="R53" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S53" s="31" t="s">
+      <c r="S53" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="T53" s="31">
+      <c r="T53" s="34">
         <f t="shared" si="3"/>
         <v>16800</v>
       </c>
-      <c r="U53" s="31">
+      <c r="U53" s="34">
         <f t="shared" si="4"/>
         <v>2520</v>
       </c>
-      <c r="V53" s="31">
+      <c r="V53" s="34">
         <f t="shared" si="5"/>
         <v>14280</v>
       </c>
@@ -5502,69 +5515,69 @@
       <c r="A54" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="B54" s="32">
+      <c r="B54" s="33">
         <v>46225</v>
       </c>
-      <c r="C54" s="31" t="s">
+      <c r="C54" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="D54" s="31" t="s">
+      <c r="D54" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E54" s="31">
+      <c r="E54" s="34">
         <v>35</v>
       </c>
-      <c r="F54" s="31" t="s">
+      <c r="F54" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="G54" s="31" t="s">
+      <c r="G54" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H54" s="31" t="s">
+      <c r="H54" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I54" s="31" t="s">
+      <c r="I54" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="J54" s="31" t="s">
+      <c r="J54" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="K54" s="31">
+      <c r="K54" s="34">
         <v>22</v>
       </c>
-      <c r="L54" s="31">
+      <c r="L54" s="34">
         <v>3500</v>
       </c>
-      <c r="M54" s="31">
+      <c r="M54" s="34">
         <v>0.2</v>
       </c>
-      <c r="N54" s="31" t="s">
+      <c r="N54" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="O54" s="31" t="s">
+      <c r="O54" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P54" s="32">
+      <c r="P54" s="33">
         <v>46226</v>
       </c>
-      <c r="Q54" s="31">
+      <c r="Q54" s="34">
         <v>5</v>
       </c>
-      <c r="R54" s="31" t="s">
+      <c r="R54" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S54" s="31" t="s">
+      <c r="S54" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="T54" s="31">
+      <c r="T54" s="34">
         <f t="shared" si="3"/>
         <v>77000</v>
       </c>
-      <c r="U54" s="31">
+      <c r="U54" s="34">
         <f t="shared" si="4"/>
         <v>15400</v>
       </c>
-      <c r="V54" s="31">
+      <c r="V54" s="34">
         <f t="shared" si="5"/>
         <v>61600</v>
       </c>
@@ -5573,69 +5586,69 @@
       <c r="A55" s="31" t="s">
         <v>181</v>
       </c>
-      <c r="B55" s="32">
+      <c r="B55" s="33">
         <v>46213</v>
       </c>
-      <c r="C55" s="31" t="s">
+      <c r="C55" s="35" t="s">
         <v>148</v>
       </c>
-      <c r="D55" s="31" t="s">
+      <c r="D55" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E55" s="31">
+      <c r="E55" s="34">
         <v>50</v>
       </c>
-      <c r="F55" s="31" t="s">
+      <c r="F55" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="G55" s="31" t="s">
+      <c r="G55" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H55" s="31" t="s">
+      <c r="H55" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I55" s="31" t="s">
+      <c r="I55" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="J55" s="31" t="s">
+      <c r="J55" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="K55" s="31">
+      <c r="K55" s="34">
         <v>4</v>
       </c>
-      <c r="L55" s="31">
+      <c r="L55" s="34">
         <v>85</v>
       </c>
-      <c r="M55" s="31">
+      <c r="M55" s="34">
         <v>0.25</v>
       </c>
-      <c r="N55" s="31" t="s">
+      <c r="N55" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O55" s="31" t="s">
+      <c r="O55" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P55" s="32">
+      <c r="P55" s="33">
         <v>46218</v>
       </c>
-      <c r="Q55" s="31">
+      <c r="Q55" s="34">
         <v>5</v>
       </c>
-      <c r="R55" s="31" t="s">
+      <c r="R55" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S55" s="31" t="s">
+      <c r="S55" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="T55" s="31">
+      <c r="T55" s="34">
         <f t="shared" si="3"/>
         <v>340</v>
       </c>
-      <c r="U55" s="31">
+      <c r="U55" s="34">
         <f t="shared" si="4"/>
         <v>85</v>
       </c>
-      <c r="V55" s="31">
+      <c r="V55" s="34">
         <f t="shared" si="5"/>
         <v>255</v>
       </c>
@@ -5644,69 +5657,69 @@
       <c r="A56" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="B56" s="32">
+      <c r="B56" s="33">
         <v>46078</v>
       </c>
-      <c r="C56" s="31" t="s">
+      <c r="C56" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="D56" s="31" t="s">
+      <c r="D56" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E56" s="31">
+      <c r="E56" s="34">
         <v>58</v>
       </c>
-      <c r="F56" s="31" t="s">
+      <c r="F56" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="G56" s="31" t="s">
+      <c r="G56" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="H56" s="31" t="s">
+      <c r="H56" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I56" s="31" t="s">
+      <c r="I56" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="J56" s="31" t="s">
+      <c r="J56" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="K56" s="31">
+      <c r="K56" s="34">
         <v>4</v>
       </c>
-      <c r="L56" s="31">
+      <c r="L56" s="34">
         <v>250</v>
       </c>
-      <c r="M56" s="31">
+      <c r="M56" s="34">
         <v>0.05</v>
       </c>
-      <c r="N56" s="31" t="s">
+      <c r="N56" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="O56" s="31" t="s">
+      <c r="O56" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P56" s="32">
+      <c r="P56" s="33">
         <v>46084</v>
       </c>
-      <c r="Q56" s="31">
+      <c r="Q56" s="34">
         <v>2</v>
       </c>
-      <c r="R56" s="31" t="s">
+      <c r="R56" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S56" s="31" t="s">
+      <c r="S56" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="T56" s="31">
+      <c r="T56" s="34">
         <f t="shared" si="3"/>
         <v>1000</v>
       </c>
-      <c r="U56" s="31">
+      <c r="U56" s="34">
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="V56" s="31">
+      <c r="V56" s="34">
         <f t="shared" si="5"/>
         <v>950</v>
       </c>
@@ -5715,69 +5728,69 @@
       <c r="A57" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="B57" s="32">
+      <c r="B57" s="33">
         <v>46204</v>
       </c>
-      <c r="C57" s="31" t="s">
+      <c r="C57" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="D57" s="31" t="s">
+      <c r="D57" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E57" s="31">
+      <c r="E57" s="34">
         <v>23</v>
       </c>
-      <c r="F57" s="31" t="s">
+      <c r="F57" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="G57" s="31" t="s">
+      <c r="G57" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H57" s="31" t="s">
+      <c r="H57" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I57" s="31" t="s">
+      <c r="I57" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="J57" s="31" t="s">
+      <c r="J57" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="K57" s="31">
+      <c r="K57" s="34">
         <v>5</v>
       </c>
-      <c r="L57" s="31">
+      <c r="L57" s="34">
         <v>750</v>
       </c>
-      <c r="M57" s="31">
+      <c r="M57" s="34">
         <v>0.25</v>
       </c>
-      <c r="N57" s="31" t="s">
+      <c r="N57" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="O57" s="31" t="s">
+      <c r="O57" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P57" s="32">
+      <c r="P57" s="33">
         <v>46209</v>
       </c>
-      <c r="Q57" s="31">
+      <c r="Q57" s="34">
         <v>1</v>
       </c>
-      <c r="R57" s="31" t="s">
+      <c r="R57" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S57" s="31" t="s">
+      <c r="S57" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="T57" s="31">
+      <c r="T57" s="34">
         <f t="shared" si="3"/>
         <v>3750</v>
       </c>
-      <c r="U57" s="31">
+      <c r="U57" s="34">
         <f t="shared" si="4"/>
         <v>937.5</v>
       </c>
-      <c r="V57" s="31">
+      <c r="V57" s="34">
         <f t="shared" si="5"/>
         <v>2812.5</v>
       </c>
@@ -5786,69 +5799,69 @@
       <c r="A58" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="B58" s="32">
+      <c r="B58" s="33">
         <v>46145</v>
       </c>
-      <c r="C58" s="31" t="s">
+      <c r="C58" s="35" t="s">
         <v>148</v>
       </c>
-      <c r="D58" s="31" t="s">
+      <c r="D58" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E58" s="31">
+      <c r="E58" s="34">
         <v>24</v>
       </c>
-      <c r="F58" s="31" t="s">
+      <c r="F58" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="G58" s="31" t="s">
+      <c r="G58" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H58" s="31" t="s">
+      <c r="H58" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I58" s="31" t="s">
+      <c r="I58" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J58" s="31" t="s">
+      <c r="J58" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="K58" s="31">
+      <c r="K58" s="34">
         <v>3</v>
       </c>
-      <c r="L58" s="31">
+      <c r="L58" s="34">
         <v>150</v>
       </c>
-      <c r="M58" s="31">
+      <c r="M58" s="34">
         <v>0.15</v>
       </c>
-      <c r="N58" s="31" t="s">
+      <c r="N58" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="O58" s="31" t="s">
+      <c r="O58" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P58" s="32">
+      <c r="P58" s="33">
         <v>46149</v>
       </c>
-      <c r="Q58" s="31">
+      <c r="Q58" s="34">
         <v>1</v>
       </c>
-      <c r="R58" s="31" t="s">
+      <c r="R58" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S58" s="31" t="s">
+      <c r="S58" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="T58" s="31">
+      <c r="T58" s="34">
         <f t="shared" si="3"/>
         <v>450</v>
       </c>
-      <c r="U58" s="31">
+      <c r="U58" s="34">
         <f t="shared" si="4"/>
         <v>67.5</v>
       </c>
-      <c r="V58" s="31">
+      <c r="V58" s="34">
         <f t="shared" si="5"/>
         <v>382.5</v>
       </c>
@@ -5857,69 +5870,69 @@
       <c r="A59" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="B59" s="32">
+      <c r="B59" s="33">
         <v>46230</v>
       </c>
-      <c r="C59" s="31" t="s">
+      <c r="C59" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="D59" s="31" t="s">
+      <c r="D59" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E59" s="31">
+      <c r="E59" s="34">
         <v>36</v>
       </c>
-      <c r="F59" s="31" t="s">
+      <c r="F59" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="G59" s="31" t="s">
+      <c r="G59" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H59" s="31" t="s">
+      <c r="H59" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I59" s="31" t="s">
+      <c r="I59" s="35" t="s">
         <v>146</v>
       </c>
-      <c r="J59" s="31" t="s">
+      <c r="J59" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="K59" s="31">
+      <c r="K59" s="34">
         <v>20</v>
       </c>
-      <c r="L59" s="31">
+      <c r="L59" s="34">
         <v>1800</v>
       </c>
-      <c r="M59" s="31">
+      <c r="M59" s="34">
         <v>0.2</v>
       </c>
-      <c r="N59" s="31" t="s">
+      <c r="N59" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O59" s="31" t="s">
+      <c r="O59" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="P59" s="32">
+      <c r="P59" s="33">
         <v>46235</v>
       </c>
-      <c r="Q59" s="31">
+      <c r="Q59" s="34">
         <v>4</v>
       </c>
-      <c r="R59" s="31" t="s">
+      <c r="R59" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S59" s="31" t="s">
+      <c r="S59" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="T59" s="31">
+      <c r="T59" s="34">
         <f t="shared" si="3"/>
         <v>36000</v>
       </c>
-      <c r="U59" s="31">
+      <c r="U59" s="34">
         <f t="shared" si="4"/>
         <v>7200</v>
       </c>
-      <c r="V59" s="31">
+      <c r="V59" s="34">
         <f t="shared" si="5"/>
         <v>28800</v>
       </c>
@@ -5928,69 +5941,69 @@
       <c r="A60" s="31" t="s">
         <v>188</v>
       </c>
-      <c r="B60" s="32">
+      <c r="B60" s="33">
         <v>46099</v>
       </c>
-      <c r="C60" s="31" t="s">
+      <c r="C60" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="D60" s="31" t="s">
+      <c r="D60" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E60" s="31">
+      <c r="E60" s="34">
         <v>40</v>
       </c>
-      <c r="F60" s="31" t="s">
+      <c r="F60" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="G60" s="31" t="s">
+      <c r="G60" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="H60" s="31" t="s">
+      <c r="H60" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I60" s="31" t="s">
+      <c r="I60" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="J60" s="31" t="s">
+      <c r="J60" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="K60" s="31">
+      <c r="K60" s="34">
         <v>24</v>
       </c>
-      <c r="L60" s="31">
+      <c r="L60" s="34">
         <v>2200</v>
       </c>
-      <c r="M60" s="31">
+      <c r="M60" s="34">
         <v>0</v>
       </c>
-      <c r="N60" s="31" t="s">
+      <c r="N60" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O60" s="31" t="s">
+      <c r="O60" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P60" s="32">
+      <c r="P60" s="33">
         <v>46106</v>
       </c>
-      <c r="Q60" s="31">
+      <c r="Q60" s="34">
         <v>3</v>
       </c>
-      <c r="R60" s="31" t="s">
+      <c r="R60" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S60" s="31" t="s">
+      <c r="S60" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="T60" s="31">
+      <c r="T60" s="34">
         <f t="shared" si="3"/>
         <v>52800</v>
       </c>
-      <c r="U60" s="31">
+      <c r="U60" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V60" s="31">
+      <c r="V60" s="34">
         <f t="shared" si="5"/>
         <v>52800</v>
       </c>
@@ -5999,69 +6012,69 @@
       <c r="A61" s="31" t="s">
         <v>188</v>
       </c>
-      <c r="B61" s="32">
+      <c r="B61" s="33">
         <v>46084</v>
       </c>
-      <c r="C61" s="31" t="s">
+      <c r="C61" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="D61" s="31" t="s">
+      <c r="D61" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E61" s="31">
+      <c r="E61" s="34">
         <v>31</v>
       </c>
-      <c r="F61" s="31" t="s">
+      <c r="F61" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="G61" s="31" t="s">
+      <c r="G61" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H61" s="31" t="s">
+      <c r="H61" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I61" s="31" t="s">
+      <c r="I61" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="J61" s="31" t="s">
+      <c r="J61" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="K61" s="31">
+      <c r="K61" s="34">
         <v>20</v>
       </c>
-      <c r="L61" s="31">
+      <c r="L61" s="34">
         <v>450</v>
       </c>
-      <c r="M61" s="31">
+      <c r="M61" s="34">
         <v>0.15</v>
       </c>
-      <c r="N61" s="31" t="s">
+      <c r="N61" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="O61" s="31" t="s">
+      <c r="O61" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P61" s="32">
+      <c r="P61" s="33">
         <v>46086</v>
       </c>
-      <c r="Q61" s="31">
+      <c r="Q61" s="34">
         <v>3</v>
       </c>
-      <c r="R61" s="31" t="s">
+      <c r="R61" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S61" s="31" t="s">
+      <c r="S61" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="T61" s="31">
+      <c r="T61" s="34">
         <f t="shared" si="3"/>
         <v>9000</v>
       </c>
-      <c r="U61" s="31">
+      <c r="U61" s="34">
         <f t="shared" si="4"/>
         <v>1350</v>
       </c>
-      <c r="V61" s="31">
+      <c r="V61" s="34">
         <f t="shared" si="5"/>
         <v>7650</v>
       </c>
@@ -6070,69 +6083,69 @@
       <c r="A62" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="B62" s="32">
+      <c r="B62" s="33">
         <v>46243</v>
       </c>
-      <c r="C62" s="31" t="s">
+      <c r="C62" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="D62" s="31" t="s">
+      <c r="D62" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E62" s="31">
+      <c r="E62" s="34">
         <v>37</v>
       </c>
-      <c r="F62" s="31" t="s">
+      <c r="F62" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="G62" s="31" t="s">
+      <c r="G62" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="H62" s="31" t="s">
+      <c r="H62" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I62" s="31" t="s">
+      <c r="I62" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="J62" s="31" t="s">
+      <c r="J62" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="K62" s="31">
+      <c r="K62" s="34">
         <v>7</v>
       </c>
-      <c r="L62" s="31">
+      <c r="L62" s="34">
         <v>250</v>
       </c>
-      <c r="M62" s="31">
+      <c r="M62" s="34">
         <v>0.15</v>
       </c>
-      <c r="N62" s="31" t="s">
+      <c r="N62" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O62" s="31" t="s">
+      <c r="O62" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P62" s="32">
+      <c r="P62" s="33">
         <v>46247</v>
       </c>
-      <c r="Q62" s="31">
+      <c r="Q62" s="34">
         <v>2</v>
       </c>
-      <c r="R62" s="31" t="s">
+      <c r="R62" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S62" s="31" t="s">
+      <c r="S62" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="T62" s="31">
+      <c r="T62" s="34">
         <f t="shared" si="3"/>
         <v>1750</v>
       </c>
-      <c r="U62" s="31">
+      <c r="U62" s="34">
         <f t="shared" si="4"/>
         <v>262.5</v>
       </c>
-      <c r="V62" s="31">
+      <c r="V62" s="34">
         <f t="shared" si="5"/>
         <v>1487.5</v>
       </c>
@@ -6141,69 +6154,69 @@
       <c r="A63" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="B63" s="32">
+      <c r="B63" s="33">
         <v>46059</v>
       </c>
-      <c r="C63" s="31" t="s">
+      <c r="C63" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="D63" s="31" t="s">
+      <c r="D63" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E63" s="31">
+      <c r="E63" s="34">
         <v>40</v>
       </c>
-      <c r="F63" s="31" t="s">
+      <c r="F63" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="G63" s="31" t="s">
+      <c r="G63" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="H63" s="31" t="s">
+      <c r="H63" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I63" s="31" t="s">
+      <c r="I63" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="J63" s="31" t="s">
+      <c r="J63" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="K63" s="31">
+      <c r="K63" s="34">
         <v>15</v>
       </c>
-      <c r="L63" s="31">
+      <c r="L63" s="34">
         <v>250</v>
       </c>
-      <c r="M63" s="31">
+      <c r="M63" s="34">
         <v>0</v>
       </c>
-      <c r="N63" s="31" t="s">
+      <c r="N63" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="O63" s="31" t="s">
+      <c r="O63" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P63" s="32">
+      <c r="P63" s="33">
         <v>46060</v>
       </c>
-      <c r="Q63" s="31">
+      <c r="Q63" s="34">
         <v>4</v>
       </c>
-      <c r="R63" s="31" t="s">
+      <c r="R63" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S63" s="31" t="s">
+      <c r="S63" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="T63" s="31">
+      <c r="T63" s="34">
         <f t="shared" si="3"/>
         <v>3750</v>
       </c>
-      <c r="U63" s="31">
+      <c r="U63" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V63" s="31">
+      <c r="V63" s="34">
         <f t="shared" si="5"/>
         <v>3750</v>
       </c>
@@ -6212,69 +6225,69 @@
       <c r="A64" s="31" t="s">
         <v>191</v>
       </c>
-      <c r="B64" s="32">
+      <c r="B64" s="33">
         <v>46161</v>
       </c>
-      <c r="C64" s="31" t="s">
+      <c r="C64" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="D64" s="31" t="s">
+      <c r="D64" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E64" s="31">
+      <c r="E64" s="34">
         <v>59</v>
       </c>
-      <c r="F64" s="31" t="s">
+      <c r="F64" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="G64" s="31" t="s">
+      <c r="G64" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H64" s="31" t="s">
+      <c r="H64" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I64" s="31" t="s">
+      <c r="I64" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="J64" s="31" t="s">
+      <c r="J64" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="K64" s="31">
+      <c r="K64" s="34">
         <v>9</v>
       </c>
-      <c r="L64" s="31">
+      <c r="L64" s="34">
         <v>85</v>
       </c>
-      <c r="M64" s="31">
+      <c r="M64" s="34">
         <v>0</v>
       </c>
-      <c r="N64" s="31" t="s">
+      <c r="N64" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O64" s="31" t="s">
+      <c r="O64" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P64" s="32">
+      <c r="P64" s="33">
         <v>46165</v>
       </c>
-      <c r="Q64" s="31">
+      <c r="Q64" s="34">
         <v>5</v>
       </c>
-      <c r="R64" s="31" t="s">
+      <c r="R64" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S64" s="31" t="s">
+      <c r="S64" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="T64" s="31">
+      <c r="T64" s="34">
         <f t="shared" si="3"/>
         <v>765</v>
       </c>
-      <c r="U64" s="31">
+      <c r="U64" s="34">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V64" s="31">
+      <c r="V64" s="34">
         <f t="shared" si="5"/>
         <v>765</v>
       </c>
@@ -6283,69 +6296,69 @@
       <c r="A65" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="B65" s="32">
+      <c r="B65" s="33">
         <v>46195</v>
       </c>
-      <c r="C65" s="31" t="s">
+      <c r="C65" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="D65" s="31" t="s">
+      <c r="D65" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E65" s="31">
+      <c r="E65" s="34">
         <v>32</v>
       </c>
-      <c r="F65" s="31" t="s">
+      <c r="F65" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="G65" s="31" t="s">
+      <c r="G65" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H65" s="31" t="s">
+      <c r="H65" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I65" s="31" t="s">
+      <c r="I65" s="35" t="s">
         <v>146</v>
       </c>
-      <c r="J65" s="31" t="s">
+      <c r="J65" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="K65" s="31">
+      <c r="K65" s="34">
         <v>6</v>
       </c>
-      <c r="L65" s="31">
+      <c r="L65" s="34">
         <v>1800</v>
       </c>
-      <c r="M65" s="31">
+      <c r="M65" s="34">
         <v>0.2</v>
       </c>
-      <c r="N65" s="31" t="s">
+      <c r="N65" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="O65" s="31" t="s">
+      <c r="O65" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P65" s="32">
+      <c r="P65" s="33">
         <v>46202</v>
       </c>
-      <c r="Q65" s="31">
+      <c r="Q65" s="34">
         <v>4</v>
       </c>
-      <c r="R65" s="31" t="s">
+      <c r="R65" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S65" s="31" t="s">
+      <c r="S65" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="T65" s="31">
+      <c r="T65" s="34">
         <f t="shared" si="3"/>
         <v>10800</v>
       </c>
-      <c r="U65" s="31">
+      <c r="U65" s="34">
         <f t="shared" si="4"/>
         <v>2160</v>
       </c>
-      <c r="V65" s="31">
+      <c r="V65" s="34">
         <f t="shared" si="5"/>
         <v>8640</v>
       </c>
@@ -6354,69 +6367,69 @@
       <c r="A66" s="31" t="s">
         <v>193</v>
       </c>
-      <c r="B66" s="32">
+      <c r="B66" s="33">
         <v>46112</v>
       </c>
-      <c r="C66" s="31" t="s">
+      <c r="C66" s="35" t="s">
         <v>148</v>
       </c>
-      <c r="D66" s="31" t="s">
+      <c r="D66" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E66" s="31">
+      <c r="E66" s="34">
         <v>27</v>
       </c>
-      <c r="F66" s="31" t="s">
+      <c r="F66" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="G66" s="31" t="s">
+      <c r="G66" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H66" s="31" t="s">
+      <c r="H66" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I66" s="31" t="s">
+      <c r="I66" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="J66" s="31" t="s">
+      <c r="J66" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="K66" s="31">
+      <c r="K66" s="34">
         <v>16</v>
       </c>
-      <c r="L66" s="31">
+      <c r="L66" s="34">
         <v>450</v>
       </c>
-      <c r="M66" s="31">
+      <c r="M66" s="34">
         <v>0.1</v>
       </c>
-      <c r="N66" s="31" t="s">
+      <c r="N66" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="O66" s="31" t="s">
+      <c r="O66" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="P66" s="32">
+      <c r="P66" s="33">
         <v>46116</v>
       </c>
-      <c r="Q66" s="31">
+      <c r="Q66" s="34">
         <v>5</v>
       </c>
-      <c r="R66" s="31" t="s">
+      <c r="R66" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S66" s="31" t="s">
+      <c r="S66" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="T66" s="31">
+      <c r="T66" s="34">
         <f t="shared" ref="T66:T101" si="6">K66*L66</f>
         <v>7200</v>
       </c>
-      <c r="U66" s="31">
+      <c r="U66" s="34">
         <f t="shared" ref="U66:U97" si="7">T66*M66</f>
         <v>720</v>
       </c>
-      <c r="V66" s="31">
+      <c r="V66" s="34">
         <f t="shared" ref="V66:V97" si="8">T66-U66</f>
         <v>6480</v>
       </c>
@@ -6425,69 +6438,69 @@
       <c r="A67" s="31" t="s">
         <v>194</v>
       </c>
-      <c r="B67" s="32">
+      <c r="B67" s="33">
         <v>46045</v>
       </c>
-      <c r="C67" s="31" t="s">
+      <c r="C67" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="D67" s="31" t="s">
+      <c r="D67" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E67" s="31">
+      <c r="E67" s="34">
         <v>28</v>
       </c>
-      <c r="F67" s="31" t="s">
+      <c r="F67" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="G67" s="31" t="s">
+      <c r="G67" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="H67" s="31" t="s">
+      <c r="H67" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I67" s="31" t="s">
+      <c r="I67" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="J67" s="31" t="s">
+      <c r="J67" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="K67" s="31">
+      <c r="K67" s="34">
         <v>1</v>
       </c>
-      <c r="L67" s="31">
+      <c r="L67" s="34">
         <v>320</v>
       </c>
-      <c r="M67" s="31">
+      <c r="M67" s="34">
         <v>0.25</v>
       </c>
-      <c r="N67" s="31" t="s">
+      <c r="N67" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="O67" s="31" t="s">
+      <c r="O67" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P67" s="32">
+      <c r="P67" s="33">
         <v>46048</v>
       </c>
-      <c r="Q67" s="31">
+      <c r="Q67" s="34">
         <v>1</v>
       </c>
-      <c r="R67" s="31" t="s">
+      <c r="R67" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S67" s="31" t="s">
+      <c r="S67" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="T67" s="31">
+      <c r="T67" s="34">
         <f t="shared" si="6"/>
         <v>320</v>
       </c>
-      <c r="U67" s="31">
+      <c r="U67" s="34">
         <f t="shared" si="7"/>
         <v>80</v>
       </c>
-      <c r="V67" s="31">
+      <c r="V67" s="34">
         <f t="shared" si="8"/>
         <v>240</v>
       </c>
@@ -6496,69 +6509,69 @@
       <c r="A68" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="B68" s="32">
+      <c r="B68" s="33">
         <v>46115</v>
       </c>
-      <c r="C68" s="31" t="s">
+      <c r="C68" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="D68" s="31" t="s">
+      <c r="D68" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E68" s="31">
+      <c r="E68" s="34">
         <v>61</v>
       </c>
-      <c r="F68" s="31" t="s">
+      <c r="F68" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="G68" s="31" t="s">
+      <c r="G68" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H68" s="31" t="s">
+      <c r="H68" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I68" s="31" t="s">
+      <c r="I68" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="J68" s="31" t="s">
+      <c r="J68" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="K68" s="31">
+      <c r="K68" s="34">
         <v>18</v>
       </c>
-      <c r="L68" s="31">
+      <c r="L68" s="34">
         <v>1200</v>
       </c>
-      <c r="M68" s="31">
+      <c r="M68" s="34">
         <v>0.05</v>
       </c>
-      <c r="N68" s="31" t="s">
+      <c r="N68" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="O68" s="31" t="s">
+      <c r="O68" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P68" s="32">
+      <c r="P68" s="33">
         <v>46120</v>
       </c>
-      <c r="Q68" s="31">
+      <c r="Q68" s="34">
         <v>4</v>
       </c>
-      <c r="R68" s="31" t="s">
+      <c r="R68" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S68" s="31" t="s">
+      <c r="S68" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="T68" s="31">
+      <c r="T68" s="34">
         <f t="shared" si="6"/>
         <v>21600</v>
       </c>
-      <c r="U68" s="31">
+      <c r="U68" s="34">
         <f t="shared" si="7"/>
         <v>1080</v>
       </c>
-      <c r="V68" s="31">
+      <c r="V68" s="34">
         <f t="shared" si="8"/>
         <v>20520</v>
       </c>
@@ -6567,69 +6580,69 @@
       <c r="A69" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="B69" s="32">
+      <c r="B69" s="33">
         <v>46184</v>
       </c>
-      <c r="C69" s="31" t="s">
+      <c r="C69" s="35" t="s">
         <v>145</v>
       </c>
-      <c r="D69" s="31" t="s">
+      <c r="D69" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E69" s="31">
+      <c r="E69" s="34">
         <v>40</v>
       </c>
-      <c r="F69" s="31" t="s">
+      <c r="F69" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="G69" s="31" t="s">
+      <c r="G69" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H69" s="31" t="s">
+      <c r="H69" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I69" s="31" t="s">
+      <c r="I69" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="J69" s="31" t="s">
+      <c r="J69" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="K69" s="31">
+      <c r="K69" s="34">
         <v>3</v>
       </c>
-      <c r="L69" s="31">
+      <c r="L69" s="34">
         <v>12500</v>
       </c>
-      <c r="M69" s="31">
+      <c r="M69" s="34">
         <v>0.05</v>
       </c>
-      <c r="N69" s="31" t="s">
+      <c r="N69" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O69" s="31" t="s">
+      <c r="O69" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P69" s="32">
+      <c r="P69" s="33">
         <v>46189</v>
       </c>
-      <c r="Q69" s="31">
+      <c r="Q69" s="34">
         <v>1</v>
       </c>
-      <c r="R69" s="31" t="s">
+      <c r="R69" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S69" s="31" t="s">
+      <c r="S69" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="T69" s="31">
+      <c r="T69" s="34">
         <f t="shared" si="6"/>
         <v>37500</v>
       </c>
-      <c r="U69" s="31">
+      <c r="U69" s="34">
         <f t="shared" si="7"/>
         <v>1875</v>
       </c>
-      <c r="V69" s="31">
+      <c r="V69" s="34">
         <f t="shared" si="8"/>
         <v>35625</v>
       </c>
@@ -6638,69 +6651,69 @@
       <c r="A70" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="B70" s="32">
+      <c r="B70" s="33">
         <v>46261</v>
       </c>
-      <c r="C70" s="31" t="s">
+      <c r="C70" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="D70" s="31" t="s">
+      <c r="D70" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E70" s="31">
+      <c r="E70" s="34">
         <v>47</v>
       </c>
-      <c r="F70" s="31" t="s">
+      <c r="F70" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="G70" s="31" t="s">
+      <c r="G70" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H70" s="31" t="s">
+      <c r="H70" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I70" s="31" t="s">
+      <c r="I70" s="35" t="s">
         <v>160</v>
       </c>
-      <c r="J70" s="31" t="s">
+      <c r="J70" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="K70" s="31">
+      <c r="K70" s="34">
         <v>18</v>
       </c>
-      <c r="L70" s="31">
+      <c r="L70" s="34">
         <v>45</v>
       </c>
-      <c r="M70" s="31">
+      <c r="M70" s="34">
         <v>0.05</v>
       </c>
-      <c r="N70" s="31" t="s">
+      <c r="N70" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="O70" s="31" t="s">
+      <c r="O70" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P70" s="32">
+      <c r="P70" s="33">
         <v>46267</v>
       </c>
-      <c r="Q70" s="31">
+      <c r="Q70" s="34">
         <v>5</v>
       </c>
-      <c r="R70" s="31" t="s">
+      <c r="R70" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S70" s="31" t="s">
+      <c r="S70" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="T70" s="31">
+      <c r="T70" s="34">
         <f t="shared" si="6"/>
         <v>810</v>
       </c>
-      <c r="U70" s="31">
+      <c r="U70" s="34">
         <f t="shared" si="7"/>
         <v>40.5</v>
       </c>
-      <c r="V70" s="31">
+      <c r="V70" s="34">
         <f t="shared" si="8"/>
         <v>769.5</v>
       </c>
@@ -6709,69 +6722,69 @@
       <c r="A71" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="B71" s="32">
+      <c r="B71" s="33">
         <v>46040</v>
       </c>
-      <c r="C71" s="31" t="s">
+      <c r="C71" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="D71" s="31" t="s">
+      <c r="D71" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E71" s="31">
+      <c r="E71" s="34">
         <v>42</v>
       </c>
-      <c r="F71" s="31" t="s">
+      <c r="F71" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="G71" s="31" t="s">
+      <c r="G71" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="H71" s="31" t="s">
+      <c r="H71" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I71" s="31" t="s">
+      <c r="I71" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="J71" s="31" t="s">
+      <c r="J71" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="K71" s="31">
+      <c r="K71" s="34">
         <v>1</v>
       </c>
-      <c r="L71" s="31">
+      <c r="L71" s="34">
         <v>750</v>
       </c>
-      <c r="M71" s="31">
+      <c r="M71" s="34">
         <v>0.1</v>
       </c>
-      <c r="N71" s="31" t="s">
+      <c r="N71" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="O71" s="31" t="s">
+      <c r="O71" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="P71" s="32">
+      <c r="P71" s="33">
         <v>46043</v>
       </c>
-      <c r="Q71" s="31">
+      <c r="Q71" s="34">
         <v>5</v>
       </c>
-      <c r="R71" s="31" t="s">
+      <c r="R71" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S71" s="31" t="s">
+      <c r="S71" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="T71" s="31">
+      <c r="T71" s="34">
         <f t="shared" si="6"/>
         <v>750</v>
       </c>
-      <c r="U71" s="31">
+      <c r="U71" s="34">
         <f t="shared" si="7"/>
         <v>75</v>
       </c>
-      <c r="V71" s="31">
+      <c r="V71" s="34">
         <f t="shared" si="8"/>
         <v>675</v>
       </c>
@@ -6780,69 +6793,69 @@
       <c r="A72" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="B72" s="32">
+      <c r="B72" s="33">
         <v>46061</v>
       </c>
-      <c r="C72" s="31" t="s">
+      <c r="C72" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="D72" s="31" t="s">
+      <c r="D72" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E72" s="31">
+      <c r="E72" s="34">
         <v>43</v>
       </c>
-      <c r="F72" s="31" t="s">
+      <c r="F72" s="32" t="s">
         <v>200</v>
       </c>
-      <c r="G72" s="31" t="s">
+      <c r="G72" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H72" s="31" t="s">
+      <c r="H72" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I72" s="31" t="s">
+      <c r="I72" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="J72" s="31" t="s">
+      <c r="J72" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="K72" s="31">
+      <c r="K72" s="34">
         <v>15</v>
       </c>
-      <c r="L72" s="31">
+      <c r="L72" s="34">
         <v>250</v>
       </c>
-      <c r="M72" s="31">
+      <c r="M72" s="34">
         <v>0.1</v>
       </c>
-      <c r="N72" s="31" t="s">
+      <c r="N72" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O72" s="31" t="s">
+      <c r="O72" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="P72" s="32">
+      <c r="P72" s="33">
         <v>46065</v>
       </c>
-      <c r="Q72" s="31">
+      <c r="Q72" s="34">
         <v>2</v>
       </c>
-      <c r="R72" s="31" t="s">
+      <c r="R72" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S72" s="31" t="s">
+      <c r="S72" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="T72" s="31">
+      <c r="T72" s="34">
         <f t="shared" si="6"/>
         <v>3750</v>
       </c>
-      <c r="U72" s="31">
+      <c r="U72" s="34">
         <f t="shared" si="7"/>
         <v>375</v>
       </c>
-      <c r="V72" s="31">
+      <c r="V72" s="34">
         <f t="shared" si="8"/>
         <v>3375</v>
       </c>
@@ -6851,69 +6864,69 @@
       <c r="A73" s="31" t="s">
         <v>201</v>
       </c>
-      <c r="B73" s="32">
+      <c r="B73" s="33">
         <v>46242</v>
       </c>
-      <c r="C73" s="31" t="s">
+      <c r="C73" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="D73" s="31" t="s">
+      <c r="D73" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E73" s="31">
+      <c r="E73" s="34">
         <v>41</v>
       </c>
-      <c r="F73" s="31" t="s">
+      <c r="F73" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="G73" s="31" t="s">
+      <c r="G73" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="H73" s="31" t="s">
+      <c r="H73" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I73" s="31" t="s">
+      <c r="I73" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="J73" s="31" t="s">
+      <c r="J73" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="K73" s="31">
+      <c r="K73" s="34">
         <v>22</v>
       </c>
-      <c r="L73" s="31">
+      <c r="L73" s="34">
         <v>450</v>
       </c>
-      <c r="M73" s="31">
+      <c r="M73" s="34">
         <v>0.25</v>
       </c>
-      <c r="N73" s="31" t="s">
+      <c r="N73" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O73" s="31" t="s">
+      <c r="O73" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P73" s="32">
+      <c r="P73" s="33">
         <v>46249</v>
       </c>
-      <c r="Q73" s="31">
+      <c r="Q73" s="34">
         <v>1</v>
       </c>
-      <c r="R73" s="31" t="s">
+      <c r="R73" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S73" s="31" t="s">
+      <c r="S73" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="T73" s="31">
+      <c r="T73" s="34">
         <f t="shared" si="6"/>
         <v>9900</v>
       </c>
-      <c r="U73" s="31">
+      <c r="U73" s="34">
         <f t="shared" si="7"/>
         <v>2475</v>
       </c>
-      <c r="V73" s="31">
+      <c r="V73" s="34">
         <f t="shared" si="8"/>
         <v>7425</v>
       </c>
@@ -6922,69 +6935,69 @@
       <c r="A74" s="31" t="s">
         <v>202</v>
       </c>
-      <c r="B74" s="32">
+      <c r="B74" s="33">
         <v>46174</v>
       </c>
-      <c r="C74" s="31" t="s">
+      <c r="C74" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D74" s="31" t="s">
+      <c r="D74" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E74" s="31">
+      <c r="E74" s="34">
         <v>27</v>
       </c>
-      <c r="F74" s="31" t="s">
+      <c r="F74" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="G74" s="31" t="s">
+      <c r="G74" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H74" s="31" t="s">
+      <c r="H74" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I74" s="31" t="s">
+      <c r="I74" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J74" s="31" t="s">
+      <c r="J74" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="K74" s="31">
+      <c r="K74" s="34">
         <v>5</v>
       </c>
-      <c r="L74" s="31">
+      <c r="L74" s="34">
         <v>150</v>
       </c>
-      <c r="M74" s="31">
+      <c r="M74" s="34">
         <v>0.15</v>
       </c>
-      <c r="N74" s="31" t="s">
+      <c r="N74" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O74" s="31" t="s">
+      <c r="O74" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P74" s="32">
+      <c r="P74" s="33">
         <v>46177</v>
       </c>
-      <c r="Q74" s="31">
+      <c r="Q74" s="34">
         <v>3</v>
       </c>
-      <c r="R74" s="31" t="s">
+      <c r="R74" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S74" s="31" t="s">
+      <c r="S74" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="T74" s="31">
+      <c r="T74" s="34">
         <f t="shared" si="6"/>
         <v>750</v>
       </c>
-      <c r="U74" s="31">
+      <c r="U74" s="34">
         <f t="shared" si="7"/>
         <v>112.5</v>
       </c>
-      <c r="V74" s="31">
+      <c r="V74" s="34">
         <f t="shared" si="8"/>
         <v>637.5</v>
       </c>
@@ -6993,69 +7006,69 @@
       <c r="A75" s="31" t="s">
         <v>203</v>
       </c>
-      <c r="B75" s="32">
+      <c r="B75" s="33">
         <v>46200</v>
       </c>
-      <c r="C75" s="31" t="s">
+      <c r="C75" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="D75" s="31" t="s">
+      <c r="D75" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E75" s="31">
+      <c r="E75" s="34">
         <v>42</v>
       </c>
-      <c r="F75" s="31" t="s">
+      <c r="F75" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="G75" s="31" t="s">
+      <c r="G75" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="H75" s="31" t="s">
+      <c r="H75" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I75" s="31" t="s">
+      <c r="I75" s="35" t="s">
         <v>146</v>
       </c>
-      <c r="J75" s="31" t="s">
+      <c r="J75" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="K75" s="31">
+      <c r="K75" s="34">
         <v>21</v>
       </c>
-      <c r="L75" s="31">
+      <c r="L75" s="34">
         <v>1800</v>
       </c>
-      <c r="M75" s="31">
+      <c r="M75" s="34">
         <v>0.25</v>
       </c>
-      <c r="N75" s="31" t="s">
+      <c r="N75" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="O75" s="31" t="s">
+      <c r="O75" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="P75" s="32">
+      <c r="P75" s="33">
         <v>46204</v>
       </c>
-      <c r="Q75" s="31">
+      <c r="Q75" s="34">
         <v>1</v>
       </c>
-      <c r="R75" s="31" t="s">
+      <c r="R75" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S75" s="31" t="s">
+      <c r="S75" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="T75" s="31">
+      <c r="T75" s="34">
         <f t="shared" si="6"/>
         <v>37800</v>
       </c>
-      <c r="U75" s="31">
+      <c r="U75" s="34">
         <f t="shared" si="7"/>
         <v>9450</v>
       </c>
-      <c r="V75" s="31">
+      <c r="V75" s="34">
         <f t="shared" si="8"/>
         <v>28350</v>
       </c>
@@ -7064,69 +7077,69 @@
       <c r="A76" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="B76" s="32">
+      <c r="B76" s="33">
         <v>46184</v>
       </c>
-      <c r="C76" s="31" t="s">
+      <c r="C76" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="D76" s="31" t="s">
+      <c r="D76" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E76" s="31">
+      <c r="E76" s="34">
         <v>26</v>
       </c>
-      <c r="F76" s="31" t="s">
+      <c r="F76" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="G76" s="31" t="s">
+      <c r="G76" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H76" s="31" t="s">
+      <c r="H76" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I76" s="31" t="s">
+      <c r="I76" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="J76" s="31" t="s">
+      <c r="J76" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="K76" s="31">
+      <c r="K76" s="34">
         <v>6</v>
       </c>
-      <c r="L76" s="31">
+      <c r="L76" s="34">
         <v>55000</v>
       </c>
-      <c r="M76" s="31">
+      <c r="M76" s="34">
         <v>0.25</v>
       </c>
-      <c r="N76" s="31" t="s">
+      <c r="N76" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="O76" s="31" t="s">
+      <c r="O76" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="P76" s="32">
+      <c r="P76" s="33">
         <v>46190</v>
       </c>
-      <c r="Q76" s="31">
+      <c r="Q76" s="34">
         <v>1</v>
       </c>
-      <c r="R76" s="31" t="s">
+      <c r="R76" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S76" s="31" t="s">
+      <c r="S76" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="T76" s="31">
+      <c r="T76" s="34">
         <f t="shared" si="6"/>
         <v>330000</v>
       </c>
-      <c r="U76" s="31">
+      <c r="U76" s="34">
         <f t="shared" si="7"/>
         <v>82500</v>
       </c>
-      <c r="V76" s="31">
+      <c r="V76" s="34">
         <f t="shared" si="8"/>
         <v>247500</v>
       </c>
@@ -7135,69 +7148,69 @@
       <c r="A77" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="B77" s="32">
+      <c r="B77" s="33">
         <v>46037</v>
       </c>
-      <c r="C77" s="31" t="s">
+      <c r="C77" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="D77" s="31" t="s">
+      <c r="D77" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E77" s="31">
+      <c r="E77" s="34">
         <v>48</v>
       </c>
-      <c r="F77" s="31" t="s">
+      <c r="F77" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="G77" s="31" t="s">
+      <c r="G77" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H77" s="31" t="s">
+      <c r="H77" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I77" s="31" t="s">
+      <c r="I77" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="J77" s="31" t="s">
+      <c r="J77" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="K77" s="31">
+      <c r="K77" s="34">
         <v>19</v>
       </c>
-      <c r="L77" s="31">
+      <c r="L77" s="34">
         <v>12500</v>
       </c>
-      <c r="M77" s="31">
+      <c r="M77" s="34">
         <v>0.25</v>
       </c>
-      <c r="N77" s="31" t="s">
+      <c r="N77" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O77" s="31" t="s">
+      <c r="O77" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P77" s="32">
+      <c r="P77" s="33">
         <v>46040</v>
       </c>
-      <c r="Q77" s="31">
+      <c r="Q77" s="34">
         <v>1</v>
       </c>
-      <c r="R77" s="31" t="s">
+      <c r="R77" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S77" s="31" t="s">
+      <c r="S77" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="T77" s="31">
+      <c r="T77" s="34">
         <f t="shared" si="6"/>
         <v>237500</v>
       </c>
-      <c r="U77" s="31">
+      <c r="U77" s="34">
         <f t="shared" si="7"/>
         <v>59375</v>
       </c>
-      <c r="V77" s="31">
+      <c r="V77" s="34">
         <f t="shared" si="8"/>
         <v>178125</v>
       </c>
@@ -7206,69 +7219,69 @@
       <c r="A78" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="B78" s="32">
+      <c r="B78" s="33">
         <v>46197</v>
       </c>
-      <c r="C78" s="31" t="s">
+      <c r="C78" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="D78" s="31" t="s">
+      <c r="D78" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E78" s="31">
+      <c r="E78" s="34">
         <v>35</v>
       </c>
-      <c r="F78" s="31" t="s">
+      <c r="F78" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="G78" s="31" t="s">
+      <c r="G78" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H78" s="31" t="s">
+      <c r="H78" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I78" s="31" t="s">
+      <c r="I78" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="J78" s="31" t="s">
+      <c r="J78" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="K78" s="31">
+      <c r="K78" s="34">
         <v>9</v>
       </c>
-      <c r="L78" s="31">
+      <c r="L78" s="34">
         <v>750</v>
       </c>
-      <c r="M78" s="31">
+      <c r="M78" s="34">
         <v>0.25</v>
       </c>
-      <c r="N78" s="31" t="s">
+      <c r="N78" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O78" s="31" t="s">
+      <c r="O78" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="P78" s="32">
+      <c r="P78" s="33">
         <v>46199</v>
       </c>
-      <c r="Q78" s="31">
+      <c r="Q78" s="34">
         <v>4</v>
       </c>
-      <c r="R78" s="31" t="s">
+      <c r="R78" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S78" s="31" t="s">
+      <c r="S78" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="T78" s="31">
+      <c r="T78" s="34">
         <f t="shared" si="6"/>
         <v>6750</v>
       </c>
-      <c r="U78" s="31">
+      <c r="U78" s="34">
         <f t="shared" si="7"/>
         <v>1687.5</v>
       </c>
-      <c r="V78" s="31">
+      <c r="V78" s="34">
         <f t="shared" si="8"/>
         <v>5062.5</v>
       </c>
@@ -7277,69 +7290,69 @@
       <c r="A79" s="31" t="s">
         <v>209</v>
       </c>
-      <c r="B79" s="32">
+      <c r="B79" s="33">
         <v>46162</v>
       </c>
-      <c r="C79" s="31" t="s">
+      <c r="C79" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="D79" s="31" t="s">
+      <c r="D79" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E79" s="31">
+      <c r="E79" s="34">
         <v>43</v>
       </c>
-      <c r="F79" s="31" t="s">
+      <c r="F79" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="G79" s="31" t="s">
+      <c r="G79" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="H79" s="31" t="s">
+      <c r="H79" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I79" s="31" t="s">
+      <c r="I79" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="J79" s="31" t="s">
+      <c r="J79" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="K79" s="31">
+      <c r="K79" s="34">
         <v>9</v>
       </c>
-      <c r="L79" s="31">
+      <c r="L79" s="34">
         <v>450</v>
       </c>
-      <c r="M79" s="31">
+      <c r="M79" s="34">
         <v>0.15</v>
       </c>
-      <c r="N79" s="31" t="s">
+      <c r="N79" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="O79" s="31" t="s">
+      <c r="O79" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P79" s="32">
+      <c r="P79" s="33">
         <v>46164</v>
       </c>
-      <c r="Q79" s="31">
+      <c r="Q79" s="34">
         <v>4</v>
       </c>
-      <c r="R79" s="31" t="s">
+      <c r="R79" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S79" s="31" t="s">
+      <c r="S79" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="T79" s="31">
+      <c r="T79" s="34">
         <f t="shared" si="6"/>
         <v>4050</v>
       </c>
-      <c r="U79" s="31">
+      <c r="U79" s="34">
         <f t="shared" si="7"/>
         <v>607.5</v>
       </c>
-      <c r="V79" s="31">
+      <c r="V79" s="34">
         <f t="shared" si="8"/>
         <v>3442.5</v>
       </c>
@@ -7348,69 +7361,69 @@
       <c r="A80" s="31" t="s">
         <v>210</v>
       </c>
-      <c r="B80" s="32">
+      <c r="B80" s="33">
         <v>46083</v>
       </c>
-      <c r="C80" s="31" t="s">
+      <c r="C80" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="D80" s="31" t="s">
+      <c r="D80" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E80" s="31">
+      <c r="E80" s="34">
         <v>57</v>
       </c>
-      <c r="F80" s="31" t="s">
+      <c r="F80" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="G80" s="31" t="s">
+      <c r="G80" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H80" s="31" t="s">
+      <c r="H80" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I80" s="31" t="s">
+      <c r="I80" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="J80" s="31" t="s">
+      <c r="J80" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="K80" s="31">
+      <c r="K80" s="34">
         <v>22</v>
       </c>
-      <c r="L80" s="31">
+      <c r="L80" s="34">
         <v>750</v>
       </c>
-      <c r="M80" s="31">
+      <c r="M80" s="34">
         <v>0.15</v>
       </c>
-      <c r="N80" s="31" t="s">
+      <c r="N80" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="O80" s="31" t="s">
+      <c r="O80" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P80" s="32">
+      <c r="P80" s="33">
         <v>46087</v>
       </c>
-      <c r="Q80" s="31">
+      <c r="Q80" s="34">
         <v>1</v>
       </c>
-      <c r="R80" s="31" t="s">
+      <c r="R80" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S80" s="31" t="s">
+      <c r="S80" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="T80" s="31">
+      <c r="T80" s="34">
         <f t="shared" si="6"/>
         <v>16500</v>
       </c>
-      <c r="U80" s="31">
+      <c r="U80" s="34">
         <f t="shared" si="7"/>
         <v>2475</v>
       </c>
-      <c r="V80" s="31">
+      <c r="V80" s="34">
         <f t="shared" si="8"/>
         <v>14025</v>
       </c>
@@ -7419,69 +7432,69 @@
       <c r="A81" s="31" t="s">
         <v>211</v>
       </c>
-      <c r="B81" s="32">
+      <c r="B81" s="33">
         <v>46254</v>
       </c>
-      <c r="C81" s="31" t="s">
+      <c r="C81" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="D81" s="31" t="s">
+      <c r="D81" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E81" s="31">
+      <c r="E81" s="34">
         <v>59</v>
       </c>
-      <c r="F81" s="31" t="s">
+      <c r="F81" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="G81" s="31" t="s">
+      <c r="G81" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="H81" s="31" t="s">
+      <c r="H81" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I81" s="31" t="s">
+      <c r="I81" s="35" t="s">
         <v>160</v>
       </c>
-      <c r="J81" s="31" t="s">
+      <c r="J81" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="K81" s="31">
+      <c r="K81" s="34">
         <v>7</v>
       </c>
-      <c r="L81" s="31">
+      <c r="L81" s="34">
         <v>45</v>
       </c>
-      <c r="M81" s="31">
+      <c r="M81" s="34">
         <v>0.2</v>
       </c>
-      <c r="N81" s="31" t="s">
+      <c r="N81" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="O81" s="31" t="s">
+      <c r="O81" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P81" s="32">
+      <c r="P81" s="33">
         <v>46257</v>
       </c>
-      <c r="Q81" s="31">
+      <c r="Q81" s="34">
         <v>2</v>
       </c>
-      <c r="R81" s="31" t="s">
+      <c r="R81" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S81" s="31" t="s">
+      <c r="S81" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="T81" s="31">
+      <c r="T81" s="34">
         <f t="shared" si="6"/>
         <v>315</v>
       </c>
-      <c r="U81" s="31">
+      <c r="U81" s="34">
         <f t="shared" si="7"/>
         <v>63</v>
       </c>
-      <c r="V81" s="31">
+      <c r="V81" s="34">
         <f t="shared" si="8"/>
         <v>252</v>
       </c>
@@ -7490,69 +7503,69 @@
       <c r="A82" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="B82" s="32">
+      <c r="B82" s="33">
         <v>46188</v>
       </c>
-      <c r="C82" s="31" t="s">
+      <c r="C82" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="D82" s="31" t="s">
+      <c r="D82" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E82" s="31">
+      <c r="E82" s="34">
         <v>23</v>
       </c>
-      <c r="F82" s="31" t="s">
+      <c r="F82" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="G82" s="31" t="s">
+      <c r="G82" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="H82" s="31" t="s">
+      <c r="H82" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I82" s="31" t="s">
+      <c r="I82" s="35" t="s">
         <v>160</v>
       </c>
-      <c r="J82" s="31" t="s">
+      <c r="J82" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="K82" s="31">
+      <c r="K82" s="34">
         <v>10</v>
       </c>
-      <c r="L82" s="31">
+      <c r="L82" s="34">
         <v>45</v>
       </c>
-      <c r="M82" s="31">
+      <c r="M82" s="34">
         <v>0.1</v>
       </c>
-      <c r="N82" s="31" t="s">
+      <c r="N82" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="O82" s="31" t="s">
+      <c r="O82" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P82" s="32">
+      <c r="P82" s="33">
         <v>46189</v>
       </c>
-      <c r="Q82" s="31">
+      <c r="Q82" s="34">
         <v>2</v>
       </c>
-      <c r="R82" s="31" t="s">
+      <c r="R82" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S82" s="31" t="s">
+      <c r="S82" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="T82" s="31">
+      <c r="T82" s="34">
         <f t="shared" si="6"/>
         <v>450</v>
       </c>
-      <c r="U82" s="31">
+      <c r="U82" s="34">
         <f t="shared" si="7"/>
         <v>45</v>
       </c>
-      <c r="V82" s="31">
+      <c r="V82" s="34">
         <f t="shared" si="8"/>
         <v>405</v>
       </c>
@@ -7561,69 +7574,69 @@
       <c r="A83" s="31" t="s">
         <v>213</v>
       </c>
-      <c r="B83" s="32">
+      <c r="B83" s="33">
         <v>46151</v>
       </c>
-      <c r="C83" s="31" t="s">
+      <c r="C83" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="D83" s="31" t="s">
+      <c r="D83" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E83" s="31">
+      <c r="E83" s="34">
         <v>51</v>
       </c>
-      <c r="F83" s="31" t="s">
+      <c r="F83" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="G83" s="31" t="s">
+      <c r="G83" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="H83" s="31" t="s">
+      <c r="H83" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I83" s="31" t="s">
+      <c r="I83" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="J83" s="31" t="s">
+      <c r="J83" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="K83" s="31">
+      <c r="K83" s="34">
         <v>4</v>
       </c>
-      <c r="L83" s="31">
+      <c r="L83" s="34">
         <v>85</v>
       </c>
-      <c r="M83" s="31">
+      <c r="M83" s="34">
         <v>0.15</v>
       </c>
-      <c r="N83" s="31" t="s">
+      <c r="N83" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O83" s="31" t="s">
+      <c r="O83" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P83" s="32">
+      <c r="P83" s="33">
         <v>46154</v>
       </c>
-      <c r="Q83" s="31">
+      <c r="Q83" s="34">
         <v>2</v>
       </c>
-      <c r="R83" s="31" t="s">
+      <c r="R83" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S83" s="31" t="s">
+      <c r="S83" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="T83" s="31">
+      <c r="T83" s="34">
         <f t="shared" si="6"/>
         <v>340</v>
       </c>
-      <c r="U83" s="31">
+      <c r="U83" s="34">
         <f t="shared" si="7"/>
         <v>51</v>
       </c>
-      <c r="V83" s="31">
+      <c r="V83" s="34">
         <f t="shared" si="8"/>
         <v>289</v>
       </c>
@@ -7632,69 +7645,69 @@
       <c r="A84" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="B84" s="32">
+      <c r="B84" s="33">
         <v>46228</v>
       </c>
-      <c r="C84" s="31" t="s">
+      <c r="C84" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="D84" s="31" t="s">
+      <c r="D84" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E84" s="31">
+      <c r="E84" s="34">
         <v>46</v>
       </c>
-      <c r="F84" s="31" t="s">
+      <c r="F84" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="G84" s="31" t="s">
+      <c r="G84" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H84" s="31" t="s">
+      <c r="H84" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I84" s="31" t="s">
+      <c r="I84" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="J84" s="31" t="s">
+      <c r="J84" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="K84" s="31">
+      <c r="K84" s="34">
         <v>15</v>
       </c>
-      <c r="L84" s="31">
+      <c r="L84" s="34">
         <v>320</v>
       </c>
-      <c r="M84" s="31">
+      <c r="M84" s="34">
         <v>0.1</v>
       </c>
-      <c r="N84" s="31" t="s">
+      <c r="N84" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="O84" s="31" t="s">
+      <c r="O84" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P84" s="32">
+      <c r="P84" s="33">
         <v>46233</v>
       </c>
-      <c r="Q84" s="31">
+      <c r="Q84" s="34">
         <v>3</v>
       </c>
-      <c r="R84" s="31" t="s">
+      <c r="R84" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S84" s="31" t="s">
+      <c r="S84" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="T84" s="31">
+      <c r="T84" s="34">
         <f t="shared" si="6"/>
         <v>4800</v>
       </c>
-      <c r="U84" s="31">
+      <c r="U84" s="34">
         <f t="shared" si="7"/>
         <v>480</v>
       </c>
-      <c r="V84" s="31">
+      <c r="V84" s="34">
         <f t="shared" si="8"/>
         <v>4320</v>
       </c>
@@ -7703,69 +7716,69 @@
       <c r="A85" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="B85" s="32">
+      <c r="B85" s="33">
         <v>46082</v>
       </c>
-      <c r="C85" s="31" t="s">
+      <c r="C85" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="D85" s="31" t="s">
+      <c r="D85" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E85" s="31">
+      <c r="E85" s="34">
         <v>60</v>
       </c>
-      <c r="F85" s="31" t="s">
+      <c r="F85" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="G85" s="31" t="s">
+      <c r="G85" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H85" s="31" t="s">
+      <c r="H85" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I85" s="31" t="s">
+      <c r="I85" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="J85" s="31" t="s">
+      <c r="J85" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="K85" s="31">
+      <c r="K85" s="34">
         <v>15</v>
       </c>
-      <c r="L85" s="31">
+      <c r="L85" s="34">
         <v>2200</v>
       </c>
-      <c r="M85" s="31">
+      <c r="M85" s="34">
         <v>0.25</v>
       </c>
-      <c r="N85" s="31" t="s">
+      <c r="N85" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="O85" s="31" t="s">
+      <c r="O85" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P85" s="32">
+      <c r="P85" s="33">
         <v>46086</v>
       </c>
-      <c r="Q85" s="31">
+      <c r="Q85" s="34">
         <v>1</v>
       </c>
-      <c r="R85" s="31" t="s">
+      <c r="R85" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S85" s="31" t="s">
+      <c r="S85" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="T85" s="31">
+      <c r="T85" s="34">
         <f t="shared" si="6"/>
         <v>33000</v>
       </c>
-      <c r="U85" s="31">
+      <c r="U85" s="34">
         <f t="shared" si="7"/>
         <v>8250</v>
       </c>
-      <c r="V85" s="31">
+      <c r="V85" s="34">
         <f t="shared" si="8"/>
         <v>24750</v>
       </c>
@@ -7774,69 +7787,69 @@
       <c r="A86" s="31" t="s">
         <v>216</v>
       </c>
-      <c r="B86" s="32">
+      <c r="B86" s="33">
         <v>46032</v>
       </c>
-      <c r="C86" s="31" t="s">
+      <c r="C86" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="D86" s="31" t="s">
+      <c r="D86" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E86" s="31">
+      <c r="E86" s="34">
         <v>27</v>
       </c>
-      <c r="F86" s="31" t="s">
+      <c r="F86" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="G86" s="31" t="s">
+      <c r="G86" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H86" s="31" t="s">
+      <c r="H86" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I86" s="31" t="s">
+      <c r="I86" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="J86" s="31" t="s">
+      <c r="J86" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="K86" s="31">
+      <c r="K86" s="34">
         <v>15</v>
       </c>
-      <c r="L86" s="31">
+      <c r="L86" s="34">
         <v>3500</v>
       </c>
-      <c r="M86" s="31">
+      <c r="M86" s="34">
         <v>0.1</v>
       </c>
-      <c r="N86" s="31" t="s">
+      <c r="N86" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="O86" s="31" t="s">
+      <c r="O86" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P86" s="32">
+      <c r="P86" s="33">
         <v>46035</v>
       </c>
-      <c r="Q86" s="31">
+      <c r="Q86" s="34">
         <v>2</v>
       </c>
-      <c r="R86" s="31" t="s">
+      <c r="R86" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S86" s="31" t="s">
+      <c r="S86" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="T86" s="31">
+      <c r="T86" s="34">
         <f t="shared" si="6"/>
         <v>52500</v>
       </c>
-      <c r="U86" s="31">
+      <c r="U86" s="34">
         <f t="shared" si="7"/>
         <v>5250</v>
       </c>
-      <c r="V86" s="31">
+      <c r="V86" s="34">
         <f t="shared" si="8"/>
         <v>47250</v>
       </c>
@@ -7845,69 +7858,69 @@
       <c r="A87" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="B87" s="32">
+      <c r="B87" s="33">
         <v>46048</v>
       </c>
-      <c r="C87" s="31" t="s">
+      <c r="C87" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="D87" s="31" t="s">
+      <c r="D87" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E87" s="31">
+      <c r="E87" s="34">
         <v>38</v>
       </c>
-      <c r="F87" s="31" t="s">
+      <c r="F87" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="G87" s="31" t="s">
+      <c r="G87" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H87" s="31" t="s">
+      <c r="H87" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I87" s="31" t="s">
+      <c r="I87" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="J87" s="31" t="s">
+      <c r="J87" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="K87" s="31">
+      <c r="K87" s="34">
         <v>15</v>
       </c>
-      <c r="L87" s="31">
+      <c r="L87" s="34">
         <v>750</v>
       </c>
-      <c r="M87" s="31">
+      <c r="M87" s="34">
         <v>0.15</v>
       </c>
-      <c r="N87" s="31" t="s">
+      <c r="N87" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O87" s="31" t="s">
+      <c r="O87" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="P87" s="32">
+      <c r="P87" s="33">
         <v>46055</v>
       </c>
-      <c r="Q87" s="31">
+      <c r="Q87" s="34">
         <v>1</v>
       </c>
-      <c r="R87" s="31" t="s">
+      <c r="R87" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S87" s="31" t="s">
+      <c r="S87" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="T87" s="31">
+      <c r="T87" s="34">
         <f t="shared" si="6"/>
         <v>11250</v>
       </c>
-      <c r="U87" s="31">
+      <c r="U87" s="34">
         <f t="shared" si="7"/>
         <v>1687.5</v>
       </c>
-      <c r="V87" s="31">
+      <c r="V87" s="34">
         <f t="shared" si="8"/>
         <v>9562.5</v>
       </c>
@@ -7916,69 +7929,69 @@
       <c r="A88" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="B88" s="32">
+      <c r="B88" s="33">
         <v>46253</v>
       </c>
-      <c r="C88" s="31" t="s">
+      <c r="C88" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="D88" s="31" t="s">
+      <c r="D88" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E88" s="31">
+      <c r="E88" s="34">
         <v>46</v>
       </c>
-      <c r="F88" s="31" t="s">
+      <c r="F88" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="G88" s="31" t="s">
+      <c r="G88" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H88" s="31" t="s">
+      <c r="H88" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I88" s="31" t="s">
+      <c r="I88" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="J88" s="31" t="s">
+      <c r="J88" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="K88" s="31">
+      <c r="K88" s="34">
         <v>15</v>
       </c>
-      <c r="L88" s="31">
+      <c r="L88" s="34">
         <v>55000</v>
       </c>
-      <c r="M88" s="31">
+      <c r="M88" s="34">
         <v>0</v>
       </c>
-      <c r="N88" s="31" t="s">
+      <c r="N88" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O88" s="31" t="s">
+      <c r="O88" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P88" s="32">
+      <c r="P88" s="33">
         <v>46259</v>
       </c>
-      <c r="Q88" s="31">
+      <c r="Q88" s="34">
         <v>5</v>
       </c>
-      <c r="R88" s="31" t="s">
+      <c r="R88" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S88" s="31" t="s">
+      <c r="S88" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="T88" s="31">
+      <c r="T88" s="34">
         <f t="shared" si="6"/>
         <v>825000</v>
       </c>
-      <c r="U88" s="31">
+      <c r="U88" s="34">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="V88" s="31">
+      <c r="V88" s="34">
         <f t="shared" si="8"/>
         <v>825000</v>
       </c>
@@ -7987,69 +8000,69 @@
       <c r="A89" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="B89" s="32">
+      <c r="B89" s="33">
         <v>46224</v>
       </c>
-      <c r="C89" s="31" t="s">
+      <c r="C89" s="35" t="s">
         <v>145</v>
       </c>
-      <c r="D89" s="31" t="s">
+      <c r="D89" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E89" s="31">
+      <c r="E89" s="34">
         <v>57</v>
       </c>
-      <c r="F89" s="31" t="s">
+      <c r="F89" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="G89" s="31" t="s">
+      <c r="G89" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H89" s="31" t="s">
+      <c r="H89" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I89" s="31" t="s">
+      <c r="I89" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="J89" s="31" t="s">
+      <c r="J89" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="K89" s="31">
+      <c r="K89" s="34">
         <v>19</v>
       </c>
-      <c r="L89" s="31">
+      <c r="L89" s="34">
         <v>12500</v>
       </c>
-      <c r="M89" s="31">
+      <c r="M89" s="34">
         <v>0.05</v>
       </c>
-      <c r="N89" s="31" t="s">
+      <c r="N89" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O89" s="31" t="s">
+      <c r="O89" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P89" s="32">
+      <c r="P89" s="33">
         <v>46227</v>
       </c>
-      <c r="Q89" s="31">
+      <c r="Q89" s="34">
         <v>2</v>
       </c>
-      <c r="R89" s="31" t="s">
+      <c r="R89" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S89" s="31" t="s">
+      <c r="S89" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="T89" s="31">
+      <c r="T89" s="34">
         <f t="shared" si="6"/>
         <v>237500</v>
       </c>
-      <c r="U89" s="31">
+      <c r="U89" s="34">
         <f t="shared" si="7"/>
         <v>11875</v>
       </c>
-      <c r="V89" s="31">
+      <c r="V89" s="34">
         <f t="shared" si="8"/>
         <v>225625</v>
       </c>
@@ -8058,69 +8071,69 @@
       <c r="A90" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="B90" s="32">
+      <c r="B90" s="33">
         <v>46242</v>
       </c>
-      <c r="C90" s="31" t="s">
+      <c r="C90" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="D90" s="31" t="s">
+      <c r="D90" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E90" s="31">
+      <c r="E90" s="34">
         <v>32</v>
       </c>
-      <c r="F90" s="31" t="s">
+      <c r="F90" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="G90" s="31" t="s">
+      <c r="G90" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H90" s="31" t="s">
+      <c r="H90" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I90" s="31" t="s">
+      <c r="I90" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="J90" s="31" t="s">
+      <c r="J90" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="K90" s="31">
+      <c r="K90" s="34">
         <v>1</v>
       </c>
-      <c r="L90" s="31">
+      <c r="L90" s="34">
         <v>2200</v>
       </c>
-      <c r="M90" s="31">
+      <c r="M90" s="34">
         <v>0.1</v>
       </c>
-      <c r="N90" s="31" t="s">
+      <c r="N90" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="O90" s="31" t="s">
+      <c r="O90" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P90" s="32">
+      <c r="P90" s="33">
         <v>46244</v>
       </c>
-      <c r="Q90" s="31">
+      <c r="Q90" s="34">
         <v>1</v>
       </c>
-      <c r="R90" s="31" t="s">
+      <c r="R90" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S90" s="31" t="s">
+      <c r="S90" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="T90" s="31">
+      <c r="T90" s="34">
         <f t="shared" si="6"/>
         <v>2200</v>
       </c>
-      <c r="U90" s="31">
+      <c r="U90" s="34">
         <f t="shared" si="7"/>
         <v>220</v>
       </c>
-      <c r="V90" s="31">
+      <c r="V90" s="34">
         <f t="shared" si="8"/>
         <v>1980</v>
       </c>
@@ -8129,69 +8142,69 @@
       <c r="A91" s="31" t="s">
         <v>221</v>
       </c>
-      <c r="B91" s="32">
+      <c r="B91" s="33">
         <v>46036</v>
       </c>
-      <c r="C91" s="31" t="s">
+      <c r="C91" s="35" t="s">
         <v>222</v>
       </c>
-      <c r="D91" s="31" t="s">
+      <c r="D91" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E91" s="31">
+      <c r="E91" s="34">
         <v>54</v>
       </c>
-      <c r="F91" s="31" t="s">
+      <c r="F91" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="G91" s="31" t="s">
+      <c r="G91" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H91" s="31" t="s">
+      <c r="H91" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I91" s="31" t="s">
+      <c r="I91" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="J91" s="31" t="s">
+      <c r="J91" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="K91" s="31">
+      <c r="K91" s="34">
         <v>15</v>
       </c>
-      <c r="L91" s="31">
+      <c r="L91" s="34">
         <v>2200</v>
       </c>
-      <c r="M91" s="31">
+      <c r="M91" s="34">
         <v>0.1</v>
       </c>
-      <c r="N91" s="31" t="s">
+      <c r="N91" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="O91" s="31" t="s">
+      <c r="O91" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P91" s="32">
+      <c r="P91" s="33">
         <v>46038</v>
       </c>
-      <c r="Q91" s="31">
+      <c r="Q91" s="34">
         <v>4</v>
       </c>
-      <c r="R91" s="31" t="s">
+      <c r="R91" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S91" s="31" t="s">
+      <c r="S91" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="T91" s="31">
+      <c r="T91" s="34">
         <f t="shared" si="6"/>
         <v>33000</v>
       </c>
-      <c r="U91" s="31">
+      <c r="U91" s="34">
         <f t="shared" si="7"/>
         <v>3300</v>
       </c>
-      <c r="V91" s="31">
+      <c r="V91" s="34">
         <f t="shared" si="8"/>
         <v>29700</v>
       </c>
@@ -8200,69 +8213,69 @@
       <c r="A92" s="31" t="s">
         <v>223</v>
       </c>
-      <c r="B92" s="32">
+      <c r="B92" s="33">
         <v>46034</v>
       </c>
-      <c r="C92" s="31" t="s">
+      <c r="C92" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="D92" s="31" t="s">
+      <c r="D92" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E92" s="31">
+      <c r="E92" s="34">
         <v>50</v>
       </c>
-      <c r="F92" s="31" t="s">
+      <c r="F92" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="G92" s="31" t="s">
+      <c r="G92" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="H92" s="31" t="s">
+      <c r="H92" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I92" s="31" t="s">
+      <c r="I92" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="J92" s="31" t="s">
+      <c r="J92" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="K92" s="31">
+      <c r="K92" s="34">
         <v>13</v>
       </c>
-      <c r="L92" s="31">
+      <c r="L92" s="34">
         <v>55000</v>
       </c>
-      <c r="M92" s="31">
+      <c r="M92" s="34">
         <v>0.15</v>
       </c>
-      <c r="N92" s="31" t="s">
+      <c r="N92" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O92" s="31" t="s">
+      <c r="O92" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P92" s="32">
+      <c r="P92" s="33">
         <v>46040</v>
       </c>
-      <c r="Q92" s="31">
+      <c r="Q92" s="34">
         <v>4</v>
       </c>
-      <c r="R92" s="31" t="s">
+      <c r="R92" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S92" s="31" t="s">
+      <c r="S92" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="T92" s="31">
+      <c r="T92" s="34">
         <f t="shared" si="6"/>
         <v>715000</v>
       </c>
-      <c r="U92" s="31">
+      <c r="U92" s="34">
         <f t="shared" si="7"/>
         <v>107250</v>
       </c>
-      <c r="V92" s="31">
+      <c r="V92" s="34">
         <f t="shared" si="8"/>
         <v>607750</v>
       </c>
@@ -8271,69 +8284,69 @@
       <c r="A93" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="B93" s="32">
+      <c r="B93" s="33">
         <v>46105</v>
       </c>
-      <c r="C93" s="31" t="s">
+      <c r="C93" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="D93" s="31" t="s">
+      <c r="D93" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E93" s="31">
+      <c r="E93" s="34">
         <v>29</v>
       </c>
-      <c r="F93" s="31" t="s">
+      <c r="F93" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="G93" s="31" t="s">
+      <c r="G93" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H93" s="31" t="s">
+      <c r="H93" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I93" s="31" t="s">
+      <c r="I93" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="J93" s="31" t="s">
+      <c r="J93" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="K93" s="31">
+      <c r="K93" s="34">
         <v>23</v>
       </c>
-      <c r="L93" s="31">
+      <c r="L93" s="34">
         <v>250</v>
       </c>
-      <c r="M93" s="31">
+      <c r="M93" s="34">
         <v>0.1</v>
       </c>
-      <c r="N93" s="31" t="s">
+      <c r="N93" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="O93" s="31" t="s">
+      <c r="O93" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="P93" s="32">
+      <c r="P93" s="33">
         <v>46110</v>
       </c>
-      <c r="Q93" s="31">
+      <c r="Q93" s="34">
         <v>5</v>
       </c>
-      <c r="R93" s="31" t="s">
+      <c r="R93" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S93" s="31" t="s">
+      <c r="S93" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="T93" s="31">
+      <c r="T93" s="34">
         <f t="shared" si="6"/>
         <v>5750</v>
       </c>
-      <c r="U93" s="31">
+      <c r="U93" s="34">
         <f t="shared" si="7"/>
         <v>575</v>
       </c>
-      <c r="V93" s="31">
+      <c r="V93" s="34">
         <f t="shared" si="8"/>
         <v>5175</v>
       </c>
@@ -8342,69 +8355,69 @@
       <c r="A94" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="B94" s="32">
+      <c r="B94" s="33">
         <v>46152</v>
       </c>
-      <c r="C94" s="31" t="s">
+      <c r="C94" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="D94" s="31" t="s">
+      <c r="D94" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E94" s="31">
+      <c r="E94" s="34">
         <v>28</v>
       </c>
-      <c r="F94" s="31" t="s">
+      <c r="F94" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="G94" s="31" t="s">
+      <c r="G94" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="H94" s="31" t="s">
+      <c r="H94" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I94" s="31" t="s">
+      <c r="I94" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="J94" s="31" t="s">
+      <c r="J94" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="K94" s="31">
+      <c r="K94" s="34">
         <v>7</v>
       </c>
-      <c r="L94" s="31">
+      <c r="L94" s="34">
         <v>250</v>
       </c>
-      <c r="M94" s="31">
+      <c r="M94" s="34">
         <v>0.15</v>
       </c>
-      <c r="N94" s="31" t="s">
+      <c r="N94" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="O94" s="31" t="s">
+      <c r="O94" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="P94" s="32">
+      <c r="P94" s="33">
         <v>46157</v>
       </c>
-      <c r="Q94" s="31">
+      <c r="Q94" s="34">
         <v>4</v>
       </c>
-      <c r="R94" s="31" t="s">
+      <c r="R94" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S94" s="31" t="s">
+      <c r="S94" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="T94" s="31">
+      <c r="T94" s="34">
         <f t="shared" si="6"/>
         <v>1750</v>
       </c>
-      <c r="U94" s="31">
+      <c r="U94" s="34">
         <f t="shared" si="7"/>
         <v>262.5</v>
       </c>
-      <c r="V94" s="31">
+      <c r="V94" s="34">
         <f t="shared" si="8"/>
         <v>1487.5</v>
       </c>
@@ -8413,69 +8426,69 @@
       <c r="A95" s="31" t="s">
         <v>226</v>
       </c>
-      <c r="B95" s="32">
+      <c r="B95" s="33">
         <v>46139</v>
       </c>
-      <c r="C95" s="31" t="s">
+      <c r="C95" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="D95" s="31" t="s">
+      <c r="D95" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E95" s="31">
+      <c r="E95" s="34">
         <v>41</v>
       </c>
-      <c r="F95" s="31" t="s">
+      <c r="F95" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="G95" s="31" t="s">
+      <c r="G95" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H95" s="31" t="s">
+      <c r="H95" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="I95" s="31" t="s">
+      <c r="I95" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="J95" s="31" t="s">
+      <c r="J95" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="K95" s="31">
+      <c r="K95" s="34">
         <v>5</v>
       </c>
-      <c r="L95" s="31">
+      <c r="L95" s="34">
         <v>85</v>
       </c>
-      <c r="M95" s="31">
+      <c r="M95" s="34">
         <v>0.25</v>
       </c>
-      <c r="N95" s="31" t="s">
+      <c r="N95" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="O95" s="31" t="s">
+      <c r="O95" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P95" s="32">
+      <c r="P95" s="33">
         <v>46143</v>
       </c>
-      <c r="Q95" s="31">
+      <c r="Q95" s="34">
         <v>1</v>
       </c>
-      <c r="R95" s="31" t="s">
+      <c r="R95" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S95" s="31" t="s">
+      <c r="S95" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="T95" s="31">
+      <c r="T95" s="34">
         <f t="shared" si="6"/>
         <v>425</v>
       </c>
-      <c r="U95" s="31">
+      <c r="U95" s="34">
         <f t="shared" si="7"/>
         <v>106.25</v>
       </c>
-      <c r="V95" s="31">
+      <c r="V95" s="34">
         <f t="shared" si="8"/>
         <v>318.75</v>
       </c>
@@ -8484,69 +8497,69 @@
       <c r="A96" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="B96" s="32">
+      <c r="B96" s="33">
         <v>46047</v>
       </c>
-      <c r="C96" s="31" t="s">
+      <c r="C96" s="35" t="s">
         <v>222</v>
       </c>
-      <c r="D96" s="31" t="s">
+      <c r="D96" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E96" s="31">
+      <c r="E96" s="34">
         <v>29</v>
       </c>
-      <c r="F96" s="31" t="s">
+      <c r="F96" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="G96" s="31" t="s">
+      <c r="G96" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H96" s="31" t="s">
+      <c r="H96" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I96" s="31" t="s">
+      <c r="I96" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="J96" s="31" t="s">
+      <c r="J96" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="K96" s="31">
+      <c r="K96" s="34">
         <v>18</v>
       </c>
-      <c r="L96" s="31">
+      <c r="L96" s="34">
         <v>12500</v>
       </c>
-      <c r="M96" s="31">
+      <c r="M96" s="34">
         <v>0.1</v>
       </c>
-      <c r="N96" s="31" t="s">
+      <c r="N96" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O96" s="31" t="s">
+      <c r="O96" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P96" s="32">
+      <c r="P96" s="33">
         <v>46053</v>
       </c>
-      <c r="Q96" s="31">
+      <c r="Q96" s="34">
         <v>4</v>
       </c>
-      <c r="R96" s="31" t="s">
+      <c r="R96" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S96" s="31" t="s">
+      <c r="S96" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="T96" s="31">
+      <c r="T96" s="34">
         <f t="shared" si="6"/>
         <v>225000</v>
       </c>
-      <c r="U96" s="31">
+      <c r="U96" s="34">
         <f t="shared" si="7"/>
         <v>22500</v>
       </c>
-      <c r="V96" s="31">
+      <c r="V96" s="34">
         <f t="shared" si="8"/>
         <v>202500</v>
       </c>
@@ -8555,69 +8568,69 @@
       <c r="A97" s="31" t="s">
         <v>228</v>
       </c>
-      <c r="B97" s="32">
+      <c r="B97" s="33">
         <v>46176</v>
       </c>
-      <c r="C97" s="31" t="s">
+      <c r="C97" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="D97" s="31" t="s">
+      <c r="D97" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E97" s="31">
+      <c r="E97" s="34">
         <v>57</v>
       </c>
-      <c r="F97" s="31" t="s">
+      <c r="F97" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="G97" s="31" t="s">
+      <c r="G97" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H97" s="31" t="s">
+      <c r="H97" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I97" s="31" t="s">
+      <c r="I97" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="J97" s="31" t="s">
+      <c r="J97" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="K97" s="31">
+      <c r="K97" s="34">
         <v>16</v>
       </c>
-      <c r="L97" s="31">
+      <c r="L97" s="34">
         <v>1200</v>
       </c>
-      <c r="M97" s="31">
+      <c r="M97" s="34">
         <v>0.05</v>
       </c>
-      <c r="N97" s="31" t="s">
+      <c r="N97" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O97" s="31" t="s">
+      <c r="O97" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P97" s="32">
+      <c r="P97" s="33">
         <v>46179</v>
       </c>
-      <c r="Q97" s="31">
+      <c r="Q97" s="34">
         <v>5</v>
       </c>
-      <c r="R97" s="31" t="s">
+      <c r="R97" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S97" s="31" t="s">
+      <c r="S97" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="T97" s="31">
+      <c r="T97" s="34">
         <f t="shared" si="6"/>
         <v>19200</v>
       </c>
-      <c r="U97" s="31">
+      <c r="U97" s="34">
         <f t="shared" si="7"/>
         <v>960</v>
       </c>
-      <c r="V97" s="31">
+      <c r="V97" s="34">
         <f t="shared" si="8"/>
         <v>18240</v>
       </c>
@@ -8626,70 +8639,70 @@
       <c r="A98" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="B98" s="32">
+      <c r="B98" s="33">
         <v>46218</v>
       </c>
-      <c r="C98" s="31" t="s">
+      <c r="C98" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="D98" s="31" t="s">
+      <c r="D98" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E98" s="31">
+      <c r="E98" s="34">
         <v>48</v>
       </c>
-      <c r="F98" s="31" t="s">
+      <c r="F98" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="G98" s="31" t="s">
+      <c r="G98" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H98" s="31" t="s">
+      <c r="H98" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I98" s="31" t="s">
+      <c r="I98" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="J98" s="31" t="s">
+      <c r="J98" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="K98" s="31">
+      <c r="K98" s="34">
         <v>21</v>
       </c>
-      <c r="L98" s="31">
+      <c r="L98" s="34">
         <v>250</v>
       </c>
-      <c r="M98" s="31">
+      <c r="M98" s="34">
         <v>0.2</v>
       </c>
-      <c r="N98" s="31" t="s">
+      <c r="N98" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O98" s="31" t="s">
+      <c r="O98" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P98" s="32">
+      <c r="P98" s="33">
         <v>46221</v>
       </c>
-      <c r="Q98" s="31">
+      <c r="Q98" s="34">
         <v>3</v>
       </c>
-      <c r="R98" s="31" t="s">
+      <c r="R98" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S98" s="31" t="s">
+      <c r="S98" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="T98" s="31">
+      <c r="T98" s="34">
         <f t="shared" si="6"/>
         <v>5250</v>
       </c>
-      <c r="U98" s="31">
-        <f t="shared" ref="U98:U129" si="9">T98*M98</f>
+      <c r="U98" s="34">
+        <f t="shared" ref="U98:U101" si="9">T98*M98</f>
         <v>1050</v>
       </c>
-      <c r="V98" s="31">
-        <f t="shared" ref="V98:V129" si="10">T98-U98</f>
+      <c r="V98" s="34">
+        <f t="shared" ref="V98:V101" si="10">T98-U98</f>
         <v>4200</v>
       </c>
     </row>
@@ -8697,69 +8710,69 @@
       <c r="A99" s="31" t="s">
         <v>230</v>
       </c>
-      <c r="B99" s="32">
+      <c r="B99" s="33">
         <v>46092</v>
       </c>
-      <c r="C99" s="31" t="s">
+      <c r="C99" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="D99" s="31" t="s">
+      <c r="D99" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E99" s="31">
+      <c r="E99" s="34">
         <v>42</v>
       </c>
-      <c r="F99" s="31" t="s">
+      <c r="F99" s="32" t="s">
         <v>200</v>
       </c>
-      <c r="G99" s="31" t="s">
+      <c r="G99" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H99" s="31" t="s">
+      <c r="H99" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I99" s="31" t="s">
+      <c r="I99" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="J99" s="31" t="s">
+      <c r="J99" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="K99" s="31">
+      <c r="K99" s="34">
         <v>5</v>
       </c>
-      <c r="L99" s="31">
+      <c r="L99" s="34">
         <v>1200</v>
       </c>
-      <c r="M99" s="31">
+      <c r="M99" s="34">
         <v>0.2</v>
       </c>
-      <c r="N99" s="31" t="s">
+      <c r="N99" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="O99" s="31" t="s">
+      <c r="O99" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P99" s="32">
+      <c r="P99" s="33">
         <v>46098</v>
       </c>
-      <c r="Q99" s="31">
+      <c r="Q99" s="34">
         <v>1</v>
       </c>
-      <c r="R99" s="31" t="s">
+      <c r="R99" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S99" s="31" t="s">
+      <c r="S99" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="T99" s="31">
+      <c r="T99" s="34">
         <f t="shared" si="6"/>
         <v>6000</v>
       </c>
-      <c r="U99" s="31">
+      <c r="U99" s="34">
         <f t="shared" si="9"/>
         <v>1200</v>
       </c>
-      <c r="V99" s="31">
+      <c r="V99" s="34">
         <f t="shared" si="10"/>
         <v>4800</v>
       </c>
@@ -8768,69 +8781,69 @@
       <c r="A100" s="31" t="s">
         <v>231</v>
       </c>
-      <c r="B100" s="32">
+      <c r="B100" s="33">
         <v>46158</v>
       </c>
-      <c r="C100" s="31" t="s">
+      <c r="C100" s="35" t="s">
         <v>153</v>
       </c>
-      <c r="D100" s="31" t="s">
+      <c r="D100" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E100" s="31">
+      <c r="E100" s="34">
         <v>50</v>
       </c>
-      <c r="F100" s="31" t="s">
+      <c r="F100" s="32" t="s">
         <v>200</v>
       </c>
-      <c r="G100" s="31" t="s">
+      <c r="G100" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H100" s="31" t="s">
+      <c r="H100" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="I100" s="31" t="s">
+      <c r="I100" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="J100" s="31" t="s">
+      <c r="J100" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="K100" s="31">
+      <c r="K100" s="34">
         <v>24</v>
       </c>
-      <c r="L100" s="31">
+      <c r="L100" s="34">
         <v>650</v>
       </c>
-      <c r="M100" s="31">
+      <c r="M100" s="34">
         <v>0.1</v>
       </c>
-      <c r="N100" s="31" t="s">
+      <c r="N100" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="O100" s="31" t="s">
+      <c r="O100" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P100" s="32">
+      <c r="P100" s="33">
         <v>46160</v>
       </c>
-      <c r="Q100" s="31">
+      <c r="Q100" s="34">
         <v>1</v>
       </c>
-      <c r="R100" s="31" t="s">
+      <c r="R100" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S100" s="31" t="s">
+      <c r="S100" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="T100" s="31">
+      <c r="T100" s="34">
         <f t="shared" si="6"/>
         <v>15600</v>
       </c>
-      <c r="U100" s="31">
+      <c r="U100" s="34">
         <f t="shared" si="9"/>
         <v>1560</v>
       </c>
-      <c r="V100" s="31">
+      <c r="V100" s="34">
         <f t="shared" si="10"/>
         <v>14040</v>
       </c>
@@ -8839,69 +8852,69 @@
       <c r="A101" s="31" t="s">
         <v>232</v>
       </c>
-      <c r="B101" s="32">
+      <c r="B101" s="33">
         <v>46216</v>
       </c>
-      <c r="C101" s="31" t="s">
+      <c r="C101" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="D101" s="31" t="s">
+      <c r="D101" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E101" s="31">
+      <c r="E101" s="34">
         <v>38</v>
       </c>
-      <c r="F101" s="31" t="s">
+      <c r="F101" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="G101" s="31" t="s">
+      <c r="G101" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="H101" s="31" t="s">
+      <c r="H101" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="I101" s="31" t="s">
+      <c r="I101" s="35" t="s">
         <v>146</v>
       </c>
-      <c r="J101" s="31" t="s">
+      <c r="J101" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="K101" s="31">
+      <c r="K101" s="34">
         <v>20</v>
       </c>
-      <c r="L101" s="31">
+      <c r="L101" s="34">
         <v>1800</v>
       </c>
-      <c r="M101" s="31">
+      <c r="M101" s="34">
         <v>0.15</v>
       </c>
-      <c r="N101" s="31" t="s">
+      <c r="N101" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="O101" s="31" t="s">
+      <c r="O101" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P101" s="32">
+      <c r="P101" s="33">
         <v>46221</v>
       </c>
-      <c r="Q101" s="31">
+      <c r="Q101" s="34">
         <v>5</v>
       </c>
-      <c r="R101" s="31" t="s">
+      <c r="R101" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="S101" s="31" t="s">
+      <c r="S101" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="T101" s="31">
+      <c r="T101" s="34">
         <f t="shared" si="6"/>
         <v>36000</v>
       </c>
-      <c r="U101" s="31">
+      <c r="U101" s="34">
         <f t="shared" si="9"/>
         <v>5400</v>
       </c>
-      <c r="V101" s="31">
+      <c r="V101" s="34">
         <f t="shared" si="10"/>
         <v>30600</v>
       </c>

--- a/Sales_Customer_Order_Management_Analysis Exersize.xlsx
+++ b/Sales_Customer_Order_Management_Analysis Exersize.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\mini project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A8594D-A8F7-4371-ACAB-70F43530E8F6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CDD411-2CCD-424C-B7BB-819FB913274C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="334">
   <si>
     <t>Excel Practical Project: Sales, Customer &amp; Order Management Analysis</t>
   </si>
@@ -1035,6 +1035,9 @@
   </si>
   <si>
     <t>4. Practical Business Questions and Answers</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -9510,6 +9513,9 @@
       <c r="A1" s="1" t="s">
         <v>290</v>
       </c>
+      <c r="C1" t="s">
+        <v>333</v>
+      </c>
     </row>
     <row r="3" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
